--- a/data/signals.xlsx
+++ b/data/signals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X377"/>
+  <dimension ref="A1:X473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30618,6 +30618,7686 @@
         <v>21</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:27.291821</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2 de Mayo - Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>90</v>
+      </c>
+      <c r="E378" t="n">
+        <v>3</v>
+      </c>
+      <c r="F378" t="n">
+        <v>6</v>
+      </c>
+      <c r="G378" t="n">
+        <v>28</v>
+      </c>
+      <c r="H378" t="n">
+        <v>13</v>
+      </c>
+      <c r="I378" t="n">
+        <v>2</v>
+      </c>
+      <c r="J378" t="n">
+        <v>2</v>
+      </c>
+      <c r="K378" t="n">
+        <v>4</v>
+      </c>
+      <c r="L378" t="n">
+        <v>11</v>
+      </c>
+      <c r="M378" t="n">
+        <v>4</v>
+      </c>
+      <c r="N378" t="n">
+        <v>1</v>
+      </c>
+      <c r="O378" t="n">
+        <v>1</v>
+      </c>
+      <c r="P378" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>17</v>
+      </c>
+      <c r="R378" t="n">
+        <v>9</v>
+      </c>
+      <c r="S378" t="n">
+        <v>1</v>
+      </c>
+      <c r="T378" t="n">
+        <v>0</v>
+      </c>
+      <c r="U378" t="n">
+        <v>0</v>
+      </c>
+      <c r="V378" t="n">
+        <v>0</v>
+      </c>
+      <c r="W378" t="n">
+        <v>0</v>
+      </c>
+      <c r="X378" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:29.053502</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Cacahuatique - Atletico Balboa</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>90</v>
+      </c>
+      <c r="E379" t="n">
+        <v>6</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>4</v>
+      </c>
+      <c r="K379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L379" t="n">
+        <v>0</v>
+      </c>
+      <c r="M379" t="n">
+        <v>0</v>
+      </c>
+      <c r="N379" t="n">
+        <v>0</v>
+      </c>
+      <c r="O379" t="n">
+        <v>2</v>
+      </c>
+      <c r="P379" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="n">
+        <v>0</v>
+      </c>
+      <c r="T379" t="n">
+        <v>0</v>
+      </c>
+      <c r="U379" t="n">
+        <v>0</v>
+      </c>
+      <c r="V379" t="n">
+        <v>0</v>
+      </c>
+      <c r="W379" t="n">
+        <v>0</v>
+      </c>
+      <c r="X379" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:31.157424</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Banfield - Sarmiento Junin</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>90</v>
+      </c>
+      <c r="E380" t="n">
+        <v>5</v>
+      </c>
+      <c r="F380" t="n">
+        <v>7</v>
+      </c>
+      <c r="G380" t="n">
+        <v>29</v>
+      </c>
+      <c r="H380" t="n">
+        <v>13</v>
+      </c>
+      <c r="I380" t="n">
+        <v>1</v>
+      </c>
+      <c r="J380" t="n">
+        <v>3</v>
+      </c>
+      <c r="K380" t="n">
+        <v>3</v>
+      </c>
+      <c r="L380" t="n">
+        <v>16</v>
+      </c>
+      <c r="M380" t="n">
+        <v>8</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
+        <v>2</v>
+      </c>
+      <c r="P380" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>13</v>
+      </c>
+      <c r="R380" t="n">
+        <v>5</v>
+      </c>
+      <c r="S380" t="n">
+        <v>1</v>
+      </c>
+      <c r="T380" t="n">
+        <v>0</v>
+      </c>
+      <c r="U380" t="n">
+        <v>0</v>
+      </c>
+      <c r="V380" t="n">
+        <v>0</v>
+      </c>
+      <c r="W380" t="n">
+        <v>0</v>
+      </c>
+      <c r="X380" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:33.249408</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>San Lorenzo - Gimnasia M.</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>90</v>
+      </c>
+      <c r="E381" t="n">
+        <v>1</v>
+      </c>
+      <c r="F381" t="n">
+        <v>9</v>
+      </c>
+      <c r="G381" t="n">
+        <v>26</v>
+      </c>
+      <c r="H381" t="n">
+        <v>8</v>
+      </c>
+      <c r="I381" t="n">
+        <v>4</v>
+      </c>
+      <c r="J381" t="n">
+        <v>1</v>
+      </c>
+      <c r="K381" t="n">
+        <v>4</v>
+      </c>
+      <c r="L381" t="n">
+        <v>13</v>
+      </c>
+      <c r="M381" t="n">
+        <v>5</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
+      <c r="P381" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>13</v>
+      </c>
+      <c r="R381" t="n">
+        <v>3</v>
+      </c>
+      <c r="S381" t="n">
+        <v>4</v>
+      </c>
+      <c r="T381" t="n">
+        <v>0</v>
+      </c>
+      <c r="U381" t="n">
+        <v>0</v>
+      </c>
+      <c r="V381" t="n">
+        <v>0</v>
+      </c>
+      <c r="W381" t="n">
+        <v>0</v>
+      </c>
+      <c r="X381" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:35.321717</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Tigre - Club Nacional</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>90</v>
+      </c>
+      <c r="E382" t="n">
+        <v>3</v>
+      </c>
+      <c r="F382" t="n">
+        <v>8</v>
+      </c>
+      <c r="G382" t="n">
+        <v>16</v>
+      </c>
+      <c r="H382" t="n">
+        <v>6</v>
+      </c>
+      <c r="I382" t="n">
+        <v>7</v>
+      </c>
+      <c r="J382" t="n">
+        <v>1</v>
+      </c>
+      <c r="K382" t="n">
+        <v>2</v>
+      </c>
+      <c r="L382" t="n">
+        <v>9</v>
+      </c>
+      <c r="M382" t="n">
+        <v>3</v>
+      </c>
+      <c r="N382" t="n">
+        <v>3</v>
+      </c>
+      <c r="O382" t="n">
+        <v>2</v>
+      </c>
+      <c r="P382" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>7</v>
+      </c>
+      <c r="R382" t="n">
+        <v>3</v>
+      </c>
+      <c r="S382" t="n">
+        <v>4</v>
+      </c>
+      <c r="T382" t="n">
+        <v>0</v>
+      </c>
+      <c r="U382" t="n">
+        <v>0</v>
+      </c>
+      <c r="V382" t="n">
+        <v>0</v>
+      </c>
+      <c r="W382" t="n">
+        <v>0</v>
+      </c>
+      <c r="X382" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:37.258555</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Juventude - Avai</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>90</v>
+      </c>
+      <c r="E383" t="n">
+        <v>1</v>
+      </c>
+      <c r="F383" t="n">
+        <v>6</v>
+      </c>
+      <c r="G383" t="n">
+        <v>19</v>
+      </c>
+      <c r="H383" t="n">
+        <v>6</v>
+      </c>
+      <c r="I383" t="n">
+        <v>3</v>
+      </c>
+      <c r="J383" t="n">
+        <v>1</v>
+      </c>
+      <c r="K383" t="n">
+        <v>3</v>
+      </c>
+      <c r="L383" t="n">
+        <v>11</v>
+      </c>
+      <c r="M383" t="n">
+        <v>6</v>
+      </c>
+      <c r="N383" t="n">
+        <v>1</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="P383" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>8</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0</v>
+      </c>
+      <c r="S383" t="n">
+        <v>2</v>
+      </c>
+      <c r="T383" t="n">
+        <v>0</v>
+      </c>
+      <c r="U383" t="n">
+        <v>0</v>
+      </c>
+      <c r="V383" t="n">
+        <v>0</v>
+      </c>
+      <c r="W383" t="n">
+        <v>0</v>
+      </c>
+      <c r="X383" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:39.624730</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Ponte Preta - Athletic Club</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>90</v>
+      </c>
+      <c r="E384" t="n">
+        <v>2</v>
+      </c>
+      <c r="F384" t="n">
+        <v>2</v>
+      </c>
+      <c r="G384" t="n">
+        <v>26</v>
+      </c>
+      <c r="H384" t="n">
+        <v>10</v>
+      </c>
+      <c r="I384" t="n">
+        <v>9</v>
+      </c>
+      <c r="J384" t="n">
+        <v>1</v>
+      </c>
+      <c r="K384" t="n">
+        <v>1</v>
+      </c>
+      <c r="L384" t="n">
+        <v>14</v>
+      </c>
+      <c r="M384" t="n">
+        <v>6</v>
+      </c>
+      <c r="N384" t="n">
+        <v>4</v>
+      </c>
+      <c r="O384" t="n">
+        <v>1</v>
+      </c>
+      <c r="P384" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>12</v>
+      </c>
+      <c r="R384" t="n">
+        <v>4</v>
+      </c>
+      <c r="S384" t="n">
+        <v>5</v>
+      </c>
+      <c r="T384" t="n">
+        <v>0</v>
+      </c>
+      <c r="U384" t="n">
+        <v>0</v>
+      </c>
+      <c r="V384" t="n">
+        <v>0</v>
+      </c>
+      <c r="W384" t="n">
+        <v>0</v>
+      </c>
+      <c r="X384" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:41.791426</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Independiente F.b.c. - Deportivo Capiata</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>90</v>
+      </c>
+      <c r="E385" t="n">
+        <v>2</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>1</v>
+      </c>
+      <c r="K385" t="n">
+        <v>0</v>
+      </c>
+      <c r="L385" t="n">
+        <v>0</v>
+      </c>
+      <c r="M385" t="n">
+        <v>0</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>1</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0</v>
+      </c>
+      <c r="S385" t="n">
+        <v>0</v>
+      </c>
+      <c r="T385" t="n">
+        <v>0</v>
+      </c>
+      <c r="U385" t="n">
+        <v>0</v>
+      </c>
+      <c r="V385" t="n">
+        <v>0</v>
+      </c>
+      <c r="W385" t="n">
+        <v>0</v>
+      </c>
+      <c r="X385" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:43.935539</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>AFC Toronto W - Calgary Wild W</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+      <c r="H386" t="n">
+        <v>0</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0</v>
+      </c>
+      <c r="K386" t="n">
+        <v>0</v>
+      </c>
+      <c r="L386" t="n">
+        <v>0</v>
+      </c>
+      <c r="M386" t="n">
+        <v>0</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" t="n">
+        <v>0</v>
+      </c>
+      <c r="T386" t="n">
+        <v>0</v>
+      </c>
+      <c r="U386" t="n">
+        <v>0</v>
+      </c>
+      <c r="V386" t="n">
+        <v>0</v>
+      </c>
+      <c r="W386" t="n">
+        <v>0</v>
+      </c>
+      <c r="X386" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:45.556890</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Quindio - Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>120</v>
+      </c>
+      <c r="E387" t="n">
+        <v>3</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="n">
+        <v>0</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>2</v>
+      </c>
+      <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="n">
+        <v>0</v>
+      </c>
+      <c r="M387" t="n">
+        <v>0</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>1</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>0</v>
+      </c>
+      <c r="R387" t="n">
+        <v>0</v>
+      </c>
+      <c r="S387" t="n">
+        <v>0</v>
+      </c>
+      <c r="T387" t="n">
+        <v>0</v>
+      </c>
+      <c r="U387" t="n">
+        <v>0</v>
+      </c>
+      <c r="V387" t="n">
+        <v>0</v>
+      </c>
+      <c r="W387" t="n">
+        <v>0</v>
+      </c>
+      <c r="X387" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:47.652257</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Bogota FC - Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>90</v>
+      </c>
+      <c r="E388" t="n">
+        <v>3</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H388" t="n">
+        <v>0</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="n">
+        <v>0</v>
+      </c>
+      <c r="M388" t="n">
+        <v>0</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
+        <v>3</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>0</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0</v>
+      </c>
+      <c r="S388" t="n">
+        <v>0</v>
+      </c>
+      <c r="T388" t="n">
+        <v>0</v>
+      </c>
+      <c r="U388" t="n">
+        <v>0</v>
+      </c>
+      <c r="V388" t="n">
+        <v>0</v>
+      </c>
+      <c r="W388" t="n">
+        <v>0</v>
+      </c>
+      <c r="X388" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:49.963428</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Verdes - CD Motagua</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>90</v>
+      </c>
+      <c r="E389" t="n">
+        <v>5</v>
+      </c>
+      <c r="F389" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" t="n">
+        <v>0</v>
+      </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="n">
+        <v>0</v>
+      </c>
+      <c r="K389" t="n">
+        <v>0</v>
+      </c>
+      <c r="L389" t="n">
+        <v>0</v>
+      </c>
+      <c r="M389" t="n">
+        <v>0</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>5</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>0</v>
+      </c>
+      <c r="R389" t="n">
+        <v>0</v>
+      </c>
+      <c r="S389" t="n">
+        <v>0</v>
+      </c>
+      <c r="T389" t="n">
+        <v>0</v>
+      </c>
+      <c r="U389" t="n">
+        <v>0</v>
+      </c>
+      <c r="V389" t="n">
+        <v>0</v>
+      </c>
+      <c r="W389" t="n">
+        <v>0</v>
+      </c>
+      <c r="X389" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:52.437543</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Argentinos JRS - Estudiantes de Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>90</v>
+      </c>
+      <c r="E390" t="n">
+        <v>3</v>
+      </c>
+      <c r="F390" t="n">
+        <v>10</v>
+      </c>
+      <c r="G390" t="n">
+        <v>29</v>
+      </c>
+      <c r="H390" t="n">
+        <v>13</v>
+      </c>
+      <c r="I390" t="n">
+        <v>1</v>
+      </c>
+      <c r="J390" t="n">
+        <v>3</v>
+      </c>
+      <c r="K390" t="n">
+        <v>6</v>
+      </c>
+      <c r="L390" t="n">
+        <v>17</v>
+      </c>
+      <c r="M390" t="n">
+        <v>9</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0</v>
+      </c>
+      <c r="P390" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>12</v>
+      </c>
+      <c r="R390" t="n">
+        <v>4</v>
+      </c>
+      <c r="S390" t="n">
+        <v>1</v>
+      </c>
+      <c r="T390" t="n">
+        <v>0</v>
+      </c>
+      <c r="U390" t="n">
+        <v>0</v>
+      </c>
+      <c r="V390" t="n">
+        <v>0</v>
+      </c>
+      <c r="W390" t="n">
+        <v>0</v>
+      </c>
+      <c r="X390" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:54.312421</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Rosario Central - Racing Club</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>90</v>
+      </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+      <c r="F391" t="n">
+        <v>8</v>
+      </c>
+      <c r="G391" t="n">
+        <v>18</v>
+      </c>
+      <c r="H391" t="n">
+        <v>3</v>
+      </c>
+      <c r="I391" t="n">
+        <v>8</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0</v>
+      </c>
+      <c r="K391" t="n">
+        <v>6</v>
+      </c>
+      <c r="L391" t="n">
+        <v>13</v>
+      </c>
+      <c r="M391" t="n">
+        <v>1</v>
+      </c>
+      <c r="N391" t="n">
+        <v>2</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>5</v>
+      </c>
+      <c r="R391" t="n">
+        <v>2</v>
+      </c>
+      <c r="S391" t="n">
+        <v>6</v>
+      </c>
+      <c r="T391" t="n">
+        <v>0</v>
+      </c>
+      <c r="U391" t="n">
+        <v>0</v>
+      </c>
+      <c r="V391" t="n">
+        <v>0</v>
+      </c>
+      <c r="W391" t="n">
+        <v>0</v>
+      </c>
+      <c r="X391" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:30:59.481306</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Fortaleza EC - Botafogo SP</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>90</v>
+      </c>
+      <c r="E392" t="n">
+        <v>1</v>
+      </c>
+      <c r="F392" t="n">
+        <v>16</v>
+      </c>
+      <c r="G392" t="n">
+        <v>27</v>
+      </c>
+      <c r="H392" t="n">
+        <v>10</v>
+      </c>
+      <c r="I392" t="n">
+        <v>2</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1</v>
+      </c>
+      <c r="K392" t="n">
+        <v>10</v>
+      </c>
+      <c r="L392" t="n">
+        <v>18</v>
+      </c>
+      <c r="M392" t="n">
+        <v>5</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" t="n">
+        <v>0</v>
+      </c>
+      <c r="P392" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>9</v>
+      </c>
+      <c r="R392" t="n">
+        <v>5</v>
+      </c>
+      <c r="S392" t="n">
+        <v>2</v>
+      </c>
+      <c r="T392" t="n">
+        <v>0</v>
+      </c>
+      <c r="U392" t="n">
+        <v>0</v>
+      </c>
+      <c r="V392" t="n">
+        <v>0</v>
+      </c>
+      <c r="W392" t="n">
+        <v>0</v>
+      </c>
+      <c r="X392" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:02.443860</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Cavalry FC - Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>90</v>
+      </c>
+      <c r="E393" t="n">
+        <v>3</v>
+      </c>
+      <c r="F393" t="n">
+        <v>16</v>
+      </c>
+      <c r="G393" t="n">
+        <v>9</v>
+      </c>
+      <c r="H393" t="n">
+        <v>12</v>
+      </c>
+      <c r="I393" t="n">
+        <v>6</v>
+      </c>
+      <c r="J393" t="n">
+        <v>2</v>
+      </c>
+      <c r="K393" t="n">
+        <v>12</v>
+      </c>
+      <c r="L393" t="n">
+        <v>3</v>
+      </c>
+      <c r="M393" t="n">
+        <v>5</v>
+      </c>
+      <c r="N393" t="n">
+        <v>4</v>
+      </c>
+      <c r="O393" t="n">
+        <v>1</v>
+      </c>
+      <c r="P393" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>6</v>
+      </c>
+      <c r="R393" t="n">
+        <v>7</v>
+      </c>
+      <c r="S393" t="n">
+        <v>2</v>
+      </c>
+      <c r="T393" t="n">
+        <v>0</v>
+      </c>
+      <c r="U393" t="n">
+        <v>0</v>
+      </c>
+      <c r="V393" t="n">
+        <v>0</v>
+      </c>
+      <c r="W393" t="n">
+        <v>0</v>
+      </c>
+      <c r="X393" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:04.620170</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Tigres FC - Atletico Nacional</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>90</v>
+      </c>
+      <c r="E394" t="n">
+        <v>2</v>
+      </c>
+      <c r="F394" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" t="n">
+        <v>0</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>2</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>0</v>
+      </c>
+      <c r="R394" t="n">
+        <v>0</v>
+      </c>
+      <c r="S394" t="n">
+        <v>0</v>
+      </c>
+      <c r="T394" t="n">
+        <v>0</v>
+      </c>
+      <c r="U394" t="n">
+        <v>0</v>
+      </c>
+      <c r="V394" t="n">
+        <v>0</v>
+      </c>
+      <c r="W394" t="n">
+        <v>0</v>
+      </c>
+      <c r="X394" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:09.728747</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>El Salvador U20 - United States U20</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>90</v>
+      </c>
+      <c r="E395" t="n">
+        <v>3</v>
+      </c>
+      <c r="F395" t="n">
+        <v>4</v>
+      </c>
+      <c r="G395" t="n">
+        <v>18</v>
+      </c>
+      <c r="H395" t="n">
+        <v>5</v>
+      </c>
+      <c r="I395" t="n">
+        <v>4</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" t="n">
+        <v>2</v>
+      </c>
+      <c r="L395" t="n">
+        <v>3</v>
+      </c>
+      <c r="M395" t="n">
+        <v>0</v>
+      </c>
+      <c r="N395" t="n">
+        <v>3</v>
+      </c>
+      <c r="O395" t="n">
+        <v>3</v>
+      </c>
+      <c r="P395" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>15</v>
+      </c>
+      <c r="R395" t="n">
+        <v>5</v>
+      </c>
+      <c r="S395" t="n">
+        <v>1</v>
+      </c>
+      <c r="T395" t="n">
+        <v>0</v>
+      </c>
+      <c r="U395" t="n">
+        <v>0</v>
+      </c>
+      <c r="V395" t="n">
+        <v>0</v>
+      </c>
+      <c r="W395" t="n">
+        <v>0</v>
+      </c>
+      <c r="X395" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:16.409268</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Diriangén - Plaza Amador</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>90</v>
+      </c>
+      <c r="E396" t="n">
+        <v>6</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" t="n">
+        <v>0</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>4</v>
+      </c>
+      <c r="K396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L396" t="n">
+        <v>0</v>
+      </c>
+      <c r="M396" t="n">
+        <v>0</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>2</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>0</v>
+      </c>
+      <c r="R396" t="n">
+        <v>0</v>
+      </c>
+      <c r="S396" t="n">
+        <v>0</v>
+      </c>
+      <c r="T396" t="n">
+        <v>0</v>
+      </c>
+      <c r="U396" t="n">
+        <v>0</v>
+      </c>
+      <c r="V396" t="n">
+        <v>0</v>
+      </c>
+      <c r="W396" t="n">
+        <v>0</v>
+      </c>
+      <c r="X396" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:19.043482</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>CD Olimpia - Mixco</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>90</v>
+      </c>
+      <c r="E397" t="n">
+        <v>2</v>
+      </c>
+      <c r="F397" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H397" t="n">
+        <v>0</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>2</v>
+      </c>
+      <c r="K397" t="n">
+        <v>0</v>
+      </c>
+      <c r="L397" t="n">
+        <v>0</v>
+      </c>
+      <c r="M397" t="n">
+        <v>0</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>0</v>
+      </c>
+      <c r="R397" t="n">
+        <v>0</v>
+      </c>
+      <c r="S397" t="n">
+        <v>0</v>
+      </c>
+      <c r="T397" t="n">
+        <v>0</v>
+      </c>
+      <c r="U397" t="n">
+        <v>0</v>
+      </c>
+      <c r="V397" t="n">
+        <v>0</v>
+      </c>
+      <c r="W397" t="n">
+        <v>0</v>
+      </c>
+      <c r="X397" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:20.919757</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Lusitânia Lourosa - FC Porto B</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>90</v>
+      </c>
+      <c r="E398" t="n">
+        <v>6</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>3</v>
+      </c>
+      <c r="K398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0</v>
+      </c>
+      <c r="M398" t="n">
+        <v>0</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>3</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>0</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0</v>
+      </c>
+      <c r="S398" t="n">
+        <v>0</v>
+      </c>
+      <c r="T398" t="n">
+        <v>0</v>
+      </c>
+      <c r="U398" t="n">
+        <v>0</v>
+      </c>
+      <c r="V398" t="n">
+        <v>0</v>
+      </c>
+      <c r="W398" t="n">
+        <v>0</v>
+      </c>
+      <c r="X398" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:23.017781</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Port FC - Persija</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>90</v>
+      </c>
+      <c r="E399" t="n">
+        <v>4</v>
+      </c>
+      <c r="F399" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0</v>
+      </c>
+      <c r="I399" t="n">
+        <v>2</v>
+      </c>
+      <c r="J399" t="n">
+        <v>2</v>
+      </c>
+      <c r="K399" t="n">
+        <v>0</v>
+      </c>
+      <c r="L399" t="n">
+        <v>0</v>
+      </c>
+      <c r="M399" t="n">
+        <v>0</v>
+      </c>
+      <c r="N399" t="n">
+        <v>1</v>
+      </c>
+      <c r="O399" t="n">
+        <v>2</v>
+      </c>
+      <c r="P399" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>0</v>
+      </c>
+      <c r="R399" t="n">
+        <v>0</v>
+      </c>
+      <c r="S399" t="n">
+        <v>1</v>
+      </c>
+      <c r="T399" t="n">
+        <v>0</v>
+      </c>
+      <c r="U399" t="n">
+        <v>0</v>
+      </c>
+      <c r="V399" t="n">
+        <v>0</v>
+      </c>
+      <c r="W399" t="n">
+        <v>0</v>
+      </c>
+      <c r="X399" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:25.453517</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Celta Vigo - Academico Viseu</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>90</v>
+      </c>
+      <c r="E400" t="n">
+        <v>4</v>
+      </c>
+      <c r="F400" t="n">
+        <v>0</v>
+      </c>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="n">
+        <v>0</v>
+      </c>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="n">
+        <v>2</v>
+      </c>
+      <c r="K400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" t="n">
+        <v>0</v>
+      </c>
+      <c r="M400" t="n">
+        <v>0</v>
+      </c>
+      <c r="N400" t="n">
+        <v>0</v>
+      </c>
+      <c r="O400" t="n">
+        <v>2</v>
+      </c>
+      <c r="P400" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>0</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0</v>
+      </c>
+      <c r="S400" t="n">
+        <v>0</v>
+      </c>
+      <c r="T400" t="n">
+        <v>0</v>
+      </c>
+      <c r="U400" t="n">
+        <v>0</v>
+      </c>
+      <c r="V400" t="n">
+        <v>0</v>
+      </c>
+      <c r="W400" t="n">
+        <v>0</v>
+      </c>
+      <c r="X400" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:27.138209</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Estrela - Portimonense</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>90</v>
+      </c>
+      <c r="E401" t="n">
+        <v>2</v>
+      </c>
+      <c r="F401" t="n">
+        <v>0</v>
+      </c>
+      <c r="G401" t="n">
+        <v>0</v>
+      </c>
+      <c r="H401" t="n">
+        <v>0</v>
+      </c>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" t="n">
+        <v>1</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" t="n">
+        <v>0</v>
+      </c>
+      <c r="M401" t="n">
+        <v>0</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>1</v>
+      </c>
+      <c r="P401" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>0</v>
+      </c>
+      <c r="R401" t="n">
+        <v>0</v>
+      </c>
+      <c r="S401" t="n">
+        <v>0</v>
+      </c>
+      <c r="T401" t="n">
+        <v>0</v>
+      </c>
+      <c r="U401" t="n">
+        <v>0</v>
+      </c>
+      <c r="V401" t="n">
+        <v>0</v>
+      </c>
+      <c r="W401" t="n">
+        <v>0</v>
+      </c>
+      <c r="X401" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:29.378812</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Brindabella - Queanbeyan City</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>90</v>
+      </c>
+      <c r="E402" t="n">
+        <v>2</v>
+      </c>
+      <c r="F402" t="n">
+        <v>0</v>
+      </c>
+      <c r="G402" t="n">
+        <v>0</v>
+      </c>
+      <c r="H402" t="n">
+        <v>0</v>
+      </c>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2</v>
+      </c>
+      <c r="K402" t="n">
+        <v>0</v>
+      </c>
+      <c r="L402" t="n">
+        <v>0</v>
+      </c>
+      <c r="M402" t="n">
+        <v>0</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>0</v>
+      </c>
+      <c r="R402" t="n">
+        <v>0</v>
+      </c>
+      <c r="S402" t="n">
+        <v>0</v>
+      </c>
+      <c r="T402" t="n">
+        <v>0</v>
+      </c>
+      <c r="U402" t="n">
+        <v>0</v>
+      </c>
+      <c r="V402" t="n">
+        <v>0</v>
+      </c>
+      <c r="W402" t="n">
+        <v>0</v>
+      </c>
+      <c r="X402" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:31.162780</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>AVS - Vianense</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>0</v>
+      </c>
+      <c r="F403" t="n">
+        <v>0</v>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0</v>
+      </c>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" t="n">
+        <v>0</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L403" t="n">
+        <v>0</v>
+      </c>
+      <c r="M403" t="n">
+        <v>0</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>0</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0</v>
+      </c>
+      <c r="S403" t="n">
+        <v>0</v>
+      </c>
+      <c r="T403" t="n">
+        <v>0</v>
+      </c>
+      <c r="U403" t="n">
+        <v>0</v>
+      </c>
+      <c r="V403" t="n">
+        <v>0</v>
+      </c>
+      <c r="W403" t="n">
+        <v>0</v>
+      </c>
+      <c r="X403" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:33.101634</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Waalwijk - Patro Eisden</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>90</v>
+      </c>
+      <c r="E404" t="n">
+        <v>3</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0</v>
+      </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" t="n">
+        <v>0</v>
+      </c>
+      <c r="I404" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" t="n">
+        <v>1</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0</v>
+      </c>
+      <c r="L404" t="n">
+        <v>0</v>
+      </c>
+      <c r="M404" t="n">
+        <v>0</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
+        <v>2</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>0</v>
+      </c>
+      <c r="R404" t="n">
+        <v>0</v>
+      </c>
+      <c r="S404" t="n">
+        <v>0</v>
+      </c>
+      <c r="T404" t="n">
+        <v>0</v>
+      </c>
+      <c r="U404" t="n">
+        <v>0</v>
+      </c>
+      <c r="V404" t="n">
+        <v>0</v>
+      </c>
+      <c r="W404" t="n">
+        <v>0</v>
+      </c>
+      <c r="X404" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:35.586434</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Tottenham - Sydney</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>120</v>
+      </c>
+      <c r="E405" t="n">
+        <v>2</v>
+      </c>
+      <c r="F405" t="n">
+        <v>7</v>
+      </c>
+      <c r="G405" t="n">
+        <v>25</v>
+      </c>
+      <c r="H405" t="n">
+        <v>8</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1</v>
+      </c>
+      <c r="J405" t="n">
+        <v>1</v>
+      </c>
+      <c r="K405" t="n">
+        <v>7</v>
+      </c>
+      <c r="L405" t="n">
+        <v>18</v>
+      </c>
+      <c r="M405" t="n">
+        <v>5</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
+        <v>1</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>7</v>
+      </c>
+      <c r="R405" t="n">
+        <v>3</v>
+      </c>
+      <c r="S405" t="n">
+        <v>1</v>
+      </c>
+      <c r="T405" t="n">
+        <v>0</v>
+      </c>
+      <c r="U405" t="n">
+        <v>0</v>
+      </c>
+      <c r="V405" t="n">
+        <v>0</v>
+      </c>
+      <c r="W405" t="n">
+        <v>0</v>
+      </c>
+      <c r="X405" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:38.388673</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka - Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>90</v>
+      </c>
+      <c r="E406" t="n">
+        <v>1</v>
+      </c>
+      <c r="F406" t="n">
+        <v>9</v>
+      </c>
+      <c r="G406" t="n">
+        <v>19</v>
+      </c>
+      <c r="H406" t="n">
+        <v>5</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1</v>
+      </c>
+      <c r="K406" t="n">
+        <v>5</v>
+      </c>
+      <c r="L406" t="n">
+        <v>12</v>
+      </c>
+      <c r="M406" t="n">
+        <v>4</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+      <c r="P406" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>7</v>
+      </c>
+      <c r="R406" t="n">
+        <v>1</v>
+      </c>
+      <c r="S406" t="n">
+        <v>1</v>
+      </c>
+      <c r="T406" t="n">
+        <v>0</v>
+      </c>
+      <c r="U406" t="n">
+        <v>0</v>
+      </c>
+      <c r="V406" t="n">
+        <v>0</v>
+      </c>
+      <c r="W406" t="n">
+        <v>0</v>
+      </c>
+      <c r="X406" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:40.101849</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa - Siheung Citizen</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>90</v>
+      </c>
+      <c r="E407" t="n">
+        <v>3</v>
+      </c>
+      <c r="F407" t="n">
+        <v>0</v>
+      </c>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="n">
+        <v>0</v>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="n">
+        <v>2</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L407" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
+        <v>1</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>0</v>
+      </c>
+      <c r="R407" t="n">
+        <v>0</v>
+      </c>
+      <c r="S407" t="n">
+        <v>0</v>
+      </c>
+      <c r="T407" t="n">
+        <v>0</v>
+      </c>
+      <c r="U407" t="n">
+        <v>0</v>
+      </c>
+      <c r="V407" t="n">
+        <v>0</v>
+      </c>
+      <c r="W407" t="n">
+        <v>0</v>
+      </c>
+      <c r="X407" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:42.983302</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Bucheon FC 1995 - Paju Citizen</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>90</v>
+      </c>
+      <c r="E408" t="n">
+        <v>3</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0</v>
+      </c>
+      <c r="G408" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" t="n">
+        <v>0</v>
+      </c>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" t="n">
+        <v>3</v>
+      </c>
+      <c r="K408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L408" t="n">
+        <v>0</v>
+      </c>
+      <c r="M408" t="n">
+        <v>0</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>0</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0</v>
+      </c>
+      <c r="S408" t="n">
+        <v>0</v>
+      </c>
+      <c r="T408" t="n">
+        <v>0</v>
+      </c>
+      <c r="U408" t="n">
+        <v>0</v>
+      </c>
+      <c r="V408" t="n">
+        <v>0</v>
+      </c>
+      <c r="W408" t="n">
+        <v>0</v>
+      </c>
+      <c r="X408" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:44.666974</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Busan I Park - FC Seoul</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>90</v>
+      </c>
+      <c r="E409" t="n">
+        <v>2</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" t="n">
+        <v>0</v>
+      </c>
+      <c r="I409" t="n">
+        <v>0</v>
+      </c>
+      <c r="J409" t="n">
+        <v>2</v>
+      </c>
+      <c r="K409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L409" t="n">
+        <v>0</v>
+      </c>
+      <c r="M409" t="n">
+        <v>0</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>0</v>
+      </c>
+      <c r="R409" t="n">
+        <v>0</v>
+      </c>
+      <c r="S409" t="n">
+        <v>0</v>
+      </c>
+      <c r="T409" t="n">
+        <v>0</v>
+      </c>
+      <c r="U409" t="n">
+        <v>0</v>
+      </c>
+      <c r="V409" t="n">
+        <v>0</v>
+      </c>
+      <c r="W409" t="n">
+        <v>0</v>
+      </c>
+      <c r="X409" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:46.680071</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Busan Transportation - Jinju Citizen</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>120</v>
+      </c>
+      <c r="E410" t="n">
+        <v>2</v>
+      </c>
+      <c r="F410" t="n">
+        <v>0</v>
+      </c>
+      <c r="G410" t="n">
+        <v>0</v>
+      </c>
+      <c r="H410" t="n">
+        <v>0</v>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>1</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="n">
+        <v>0</v>
+      </c>
+      <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>1</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>0</v>
+      </c>
+      <c r="R410" t="n">
+        <v>0</v>
+      </c>
+      <c r="S410" t="n">
+        <v>0</v>
+      </c>
+      <c r="T410" t="n">
+        <v>0</v>
+      </c>
+      <c r="U410" t="n">
+        <v>0</v>
+      </c>
+      <c r="V410" t="n">
+        <v>0</v>
+      </c>
+      <c r="W410" t="n">
+        <v>0</v>
+      </c>
+      <c r="X410" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:49.373000</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Gimcheon Sangmu FC - Suwon City FC</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>90</v>
+      </c>
+      <c r="E411" t="n">
+        <v>3</v>
+      </c>
+      <c r="F411" t="n">
+        <v>0</v>
+      </c>
+      <c r="G411" t="n">
+        <v>0</v>
+      </c>
+      <c r="H411" t="n">
+        <v>0</v>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="n">
+        <v>2</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L411" t="n">
+        <v>0</v>
+      </c>
+      <c r="M411" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>1</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>0</v>
+      </c>
+      <c r="R411" t="n">
+        <v>0</v>
+      </c>
+      <c r="S411" t="n">
+        <v>0</v>
+      </c>
+      <c r="T411" t="n">
+        <v>0</v>
+      </c>
+      <c r="U411" t="n">
+        <v>0</v>
+      </c>
+      <c r="V411" t="n">
+        <v>0</v>
+      </c>
+      <c r="W411" t="n">
+        <v>0</v>
+      </c>
+      <c r="X411" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:52.598664</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen - Incheon United</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>90</v>
+      </c>
+      <c r="E412" t="n">
+        <v>1</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L412" t="n">
+        <v>0</v>
+      </c>
+      <c r="M412" t="n">
+        <v>0</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>0</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
+      <c r="S412" t="n">
+        <v>0</v>
+      </c>
+      <c r="T412" t="n">
+        <v>0</v>
+      </c>
+      <c r="U412" t="n">
+        <v>0</v>
+      </c>
+      <c r="V412" t="n">
+        <v>0</v>
+      </c>
+      <c r="W412" t="n">
+        <v>0</v>
+      </c>
+      <c r="X412" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:55.013611</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Gwangju FC - Cheonan City</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>90</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1</v>
+      </c>
+      <c r="F413" t="n">
+        <v>0</v>
+      </c>
+      <c r="G413" t="n">
+        <v>0</v>
+      </c>
+      <c r="H413" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" t="n">
+        <v>1</v>
+      </c>
+      <c r="K413" t="n">
+        <v>0</v>
+      </c>
+      <c r="L413" t="n">
+        <v>0</v>
+      </c>
+      <c r="M413" t="n">
+        <v>0</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>0</v>
+      </c>
+      <c r="R413" t="n">
+        <v>0</v>
+      </c>
+      <c r="S413" t="n">
+        <v>0</v>
+      </c>
+      <c r="T413" t="n">
+        <v>0</v>
+      </c>
+      <c r="U413" t="n">
+        <v>0</v>
+      </c>
+      <c r="V413" t="n">
+        <v>0</v>
+      </c>
+      <c r="W413" t="n">
+        <v>0</v>
+      </c>
+      <c r="X413" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:57.280291</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Ulsan Citizen - Ulsan Hyundai FC</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>90</v>
+      </c>
+      <c r="E414" t="n">
+        <v>1</v>
+      </c>
+      <c r="F414" t="n">
+        <v>0</v>
+      </c>
+      <c r="G414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" t="n">
+        <v>0</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" t="n">
+        <v>0</v>
+      </c>
+      <c r="M414" t="n">
+        <v>0</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="n">
+        <v>0</v>
+      </c>
+      <c r="T414" t="n">
+        <v>0</v>
+      </c>
+      <c r="U414" t="n">
+        <v>0</v>
+      </c>
+      <c r="V414" t="n">
+        <v>0</v>
+      </c>
+      <c r="W414" t="n">
+        <v>0</v>
+      </c>
+      <c r="X414" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:31:59.525881</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Yeoju Sejong - Dangjin Citizen</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>90</v>
+      </c>
+      <c r="E415" t="n">
+        <v>1</v>
+      </c>
+      <c r="F415" t="n">
+        <v>0</v>
+      </c>
+      <c r="G415" t="n">
+        <v>0</v>
+      </c>
+      <c r="H415" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" t="n">
+        <v>0</v>
+      </c>
+      <c r="M415" t="n">
+        <v>0</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" t="n">
+        <v>1</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>0</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0</v>
+      </c>
+      <c r="S415" t="n">
+        <v>0</v>
+      </c>
+      <c r="T415" t="n">
+        <v>0</v>
+      </c>
+      <c r="U415" t="n">
+        <v>0</v>
+      </c>
+      <c r="V415" t="n">
+        <v>0</v>
+      </c>
+      <c r="W415" t="n">
+        <v>0</v>
+      </c>
+      <c r="X415" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:01.786196</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Cheongju - FC Anyang</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>90</v>
+      </c>
+      <c r="E416" t="n">
+        <v>4</v>
+      </c>
+      <c r="F416" t="n">
+        <v>0</v>
+      </c>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
+      <c r="H416" t="n">
+        <v>0</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1</v>
+      </c>
+      <c r="K416" t="n">
+        <v>0</v>
+      </c>
+      <c r="L416" t="n">
+        <v>0</v>
+      </c>
+      <c r="M416" t="n">
+        <v>0</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>3</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>0</v>
+      </c>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
+      <c r="S416" t="n">
+        <v>0</v>
+      </c>
+      <c r="T416" t="n">
+        <v>0</v>
+      </c>
+      <c r="U416" t="n">
+        <v>0</v>
+      </c>
+      <c r="V416" t="n">
+        <v>0</v>
+      </c>
+      <c r="W416" t="n">
+        <v>0</v>
+      </c>
+      <c r="X416" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:03.609258</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Jeju United FC - Hwaseong</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>120</v>
+      </c>
+      <c r="E417" t="n">
+        <v>6</v>
+      </c>
+      <c r="F417" t="n">
+        <v>0</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="n">
+        <v>0</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" t="n">
+        <v>3</v>
+      </c>
+      <c r="K417" t="n">
+        <v>0</v>
+      </c>
+      <c r="L417" t="n">
+        <v>0</v>
+      </c>
+      <c r="M417" t="n">
+        <v>0</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>3</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>0</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0</v>
+      </c>
+      <c r="S417" t="n">
+        <v>0</v>
+      </c>
+      <c r="T417" t="n">
+        <v>0</v>
+      </c>
+      <c r="U417" t="n">
+        <v>0</v>
+      </c>
+      <c r="V417" t="n">
+        <v>0</v>
+      </c>
+      <c r="W417" t="n">
+        <v>0</v>
+      </c>
+      <c r="X417" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:06.229036</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>BIT - Nantong Haimen Codion</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>90</v>
+      </c>
+      <c r="E418" t="n">
+        <v>3</v>
+      </c>
+      <c r="F418" t="n">
+        <v>0</v>
+      </c>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="n">
+        <v>0</v>
+      </c>
+      <c r="I418" t="n">
+        <v>4</v>
+      </c>
+      <c r="J418" t="n">
+        <v>1</v>
+      </c>
+      <c r="K418" t="n">
+        <v>0</v>
+      </c>
+      <c r="L418" t="n">
+        <v>0</v>
+      </c>
+      <c r="M418" t="n">
+        <v>0</v>
+      </c>
+      <c r="N418" t="n">
+        <v>3</v>
+      </c>
+      <c r="O418" t="n">
+        <v>2</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>0</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0</v>
+      </c>
+      <c r="S418" t="n">
+        <v>1</v>
+      </c>
+      <c r="T418" t="n">
+        <v>0</v>
+      </c>
+      <c r="U418" t="n">
+        <v>0</v>
+      </c>
+      <c r="V418" t="n">
+        <v>0</v>
+      </c>
+      <c r="W418" t="n">
+        <v>0</v>
+      </c>
+      <c r="X418" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:09.225065</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Åsane U19 - Sandefjord U19</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>0</v>
+      </c>
+      <c r="F419" t="n">
+        <v>0</v>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0</v>
+      </c>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" t="n">
+        <v>0</v>
+      </c>
+      <c r="M419" t="n">
+        <v>0</v>
+      </c>
+      <c r="N419" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>0</v>
+      </c>
+      <c r="R419" t="n">
+        <v>0</v>
+      </c>
+      <c r="S419" t="n">
+        <v>0</v>
+      </c>
+      <c r="T419" t="n">
+        <v>0</v>
+      </c>
+      <c r="U419" t="n">
+        <v>0</v>
+      </c>
+      <c r="V419" t="n">
+        <v>0</v>
+      </c>
+      <c r="W419" t="n">
+        <v>0</v>
+      </c>
+      <c r="X419" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:11.335545</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Cardiff City U21 - Manchester City U21</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="n">
+        <v>0</v>
+      </c>
+      <c r="M420" t="n">
+        <v>0</v>
+      </c>
+      <c r="N420" t="n">
+        <v>0</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+      <c r="P420" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>0</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0</v>
+      </c>
+      <c r="S420" t="n">
+        <v>0</v>
+      </c>
+      <c r="T420" t="n">
+        <v>0</v>
+      </c>
+      <c r="U420" t="n">
+        <v>0</v>
+      </c>
+      <c r="V420" t="n">
+        <v>0</v>
+      </c>
+      <c r="W420" t="n">
+        <v>0</v>
+      </c>
+      <c r="X420" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:13.083547</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Gimhae City - Seongnam FC</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>90</v>
+      </c>
+      <c r="E421" t="n">
+        <v>1</v>
+      </c>
+      <c r="F421" t="n">
+        <v>0</v>
+      </c>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" t="n">
+        <v>0</v>
+      </c>
+      <c r="I421" t="n">
+        <v>0</v>
+      </c>
+      <c r="J421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" t="n">
+        <v>0</v>
+      </c>
+      <c r="L421" t="n">
+        <v>0</v>
+      </c>
+      <c r="M421" t="n">
+        <v>0</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>1</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>0</v>
+      </c>
+      <c r="R421" t="n">
+        <v>0</v>
+      </c>
+      <c r="S421" t="n">
+        <v>0</v>
+      </c>
+      <c r="T421" t="n">
+        <v>0</v>
+      </c>
+      <c r="U421" t="n">
+        <v>0</v>
+      </c>
+      <c r="V421" t="n">
+        <v>0</v>
+      </c>
+      <c r="W421" t="n">
+        <v>0</v>
+      </c>
+      <c r="X421" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:15.172868</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Rizhao Yuqi - Tai'an Tiankuang</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>90</v>
+      </c>
+      <c r="E422" t="n">
+        <v>4</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0</v>
+      </c>
+      <c r="G422" t="n">
+        <v>0</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0</v>
+      </c>
+      <c r="I422" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" t="n">
+        <v>2</v>
+      </c>
+      <c r="K422" t="n">
+        <v>0</v>
+      </c>
+      <c r="L422" t="n">
+        <v>0</v>
+      </c>
+      <c r="M422" t="n">
+        <v>0</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>2</v>
+      </c>
+      <c r="P422" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>0</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0</v>
+      </c>
+      <c r="S422" t="n">
+        <v>0</v>
+      </c>
+      <c r="T422" t="n">
+        <v>0</v>
+      </c>
+      <c r="U422" t="n">
+        <v>0</v>
+      </c>
+      <c r="V422" t="n">
+        <v>0</v>
+      </c>
+      <c r="W422" t="n">
+        <v>0</v>
+      </c>
+      <c r="X422" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:17.247137</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Wuhan Three Towns II - Xiamen Feilu</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>90</v>
+      </c>
+      <c r="E423" t="n">
+        <v>3</v>
+      </c>
+      <c r="F423" t="n">
+        <v>0</v>
+      </c>
+      <c r="G423" t="n">
+        <v>0</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0</v>
+      </c>
+      <c r="I423" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" t="n">
+        <v>2</v>
+      </c>
+      <c r="K423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" t="n">
+        <v>0</v>
+      </c>
+      <c r="M423" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>1</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>0</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0</v>
+      </c>
+      <c r="S423" t="n">
+        <v>0</v>
+      </c>
+      <c r="T423" t="n">
+        <v>0</v>
+      </c>
+      <c r="U423" t="n">
+        <v>0</v>
+      </c>
+      <c r="V423" t="n">
+        <v>0</v>
+      </c>
+      <c r="W423" t="n">
+        <v>0</v>
+      </c>
+      <c r="X423" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:19.753121</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Leixoes - Vizela</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>0</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" t="n">
+        <v>0</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" t="n">
+        <v>0</v>
+      </c>
+      <c r="K424" t="n">
+        <v>0</v>
+      </c>
+      <c r="L424" t="n">
+        <v>0</v>
+      </c>
+      <c r="M424" t="n">
+        <v>0</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" t="n">
+        <v>0</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>0</v>
+      </c>
+      <c r="R424" t="n">
+        <v>0</v>
+      </c>
+      <c r="S424" t="n">
+        <v>0</v>
+      </c>
+      <c r="T424" t="n">
+        <v>0</v>
+      </c>
+      <c r="U424" t="n">
+        <v>0</v>
+      </c>
+      <c r="V424" t="n">
+        <v>0</v>
+      </c>
+      <c r="W424" t="n">
+        <v>0</v>
+      </c>
+      <c r="X424" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:21.990690</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Pogoń Szczecin II - Carina Gubin</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>0</v>
+      </c>
+      <c r="F425" t="n">
+        <v>0</v>
+      </c>
+      <c r="G425" t="n">
+        <v>0</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0</v>
+      </c>
+      <c r="J425" t="n">
+        <v>0</v>
+      </c>
+      <c r="K425" t="n">
+        <v>0</v>
+      </c>
+      <c r="L425" t="n">
+        <v>0</v>
+      </c>
+      <c r="M425" t="n">
+        <v>0</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>0</v>
+      </c>
+      <c r="R425" t="n">
+        <v>0</v>
+      </c>
+      <c r="S425" t="n">
+        <v>0</v>
+      </c>
+      <c r="T425" t="n">
+        <v>0</v>
+      </c>
+      <c r="U425" t="n">
+        <v>0</v>
+      </c>
+      <c r="V425" t="n">
+        <v>0</v>
+      </c>
+      <c r="W425" t="n">
+        <v>0</v>
+      </c>
+      <c r="X425" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:24.396419</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Waalwijk - Telstar</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>0</v>
+      </c>
+      <c r="F426" t="n">
+        <v>0</v>
+      </c>
+      <c r="G426" t="n">
+        <v>0</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0</v>
+      </c>
+      <c r="I426" t="n">
+        <v>0</v>
+      </c>
+      <c r="J426" t="n">
+        <v>0</v>
+      </c>
+      <c r="K426" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" t="n">
+        <v>0</v>
+      </c>
+      <c r="N426" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>0</v>
+      </c>
+      <c r="R426" t="n">
+        <v>0</v>
+      </c>
+      <c r="S426" t="n">
+        <v>0</v>
+      </c>
+      <c r="T426" t="n">
+        <v>0</v>
+      </c>
+      <c r="U426" t="n">
+        <v>0</v>
+      </c>
+      <c r="V426" t="n">
+        <v>0</v>
+      </c>
+      <c r="W426" t="n">
+        <v>0</v>
+      </c>
+      <c r="X426" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:27.225070</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Pacos Ferreira - Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>0</v>
+      </c>
+      <c r="F427" t="n">
+        <v>0</v>
+      </c>
+      <c r="G427" t="n">
+        <v>0</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0</v>
+      </c>
+      <c r="I427" t="n">
+        <v>0</v>
+      </c>
+      <c r="J427" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" t="n">
+        <v>0</v>
+      </c>
+      <c r="L427" t="n">
+        <v>0</v>
+      </c>
+      <c r="M427" t="n">
+        <v>0</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>0</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0</v>
+      </c>
+      <c r="S427" t="n">
+        <v>0</v>
+      </c>
+      <c r="T427" t="n">
+        <v>0</v>
+      </c>
+      <c r="U427" t="n">
+        <v>0</v>
+      </c>
+      <c r="V427" t="n">
+        <v>0</v>
+      </c>
+      <c r="W427" t="n">
+        <v>0</v>
+      </c>
+      <c r="X427" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:28.827411</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Tondela - São João Ver</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>90</v>
+      </c>
+      <c r="E428" t="n">
+        <v>2</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0</v>
+      </c>
+      <c r="I428" t="n">
+        <v>0</v>
+      </c>
+      <c r="J428" t="n">
+        <v>1</v>
+      </c>
+      <c r="K428" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" t="n">
+        <v>0</v>
+      </c>
+      <c r="M428" t="n">
+        <v>0</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>1</v>
+      </c>
+      <c r="P428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>0</v>
+      </c>
+      <c r="R428" t="n">
+        <v>0</v>
+      </c>
+      <c r="S428" t="n">
+        <v>0</v>
+      </c>
+      <c r="T428" t="n">
+        <v>0</v>
+      </c>
+      <c r="U428" t="n">
+        <v>0</v>
+      </c>
+      <c r="V428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W428" t="n">
+        <v>0</v>
+      </c>
+      <c r="X428" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:30.934501</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Alverca - Academica</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>0</v>
+      </c>
+      <c r="F429" t="n">
+        <v>0</v>
+      </c>
+      <c r="G429" t="n">
+        <v>0</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0</v>
+      </c>
+      <c r="I429" t="n">
+        <v>0</v>
+      </c>
+      <c r="J429" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="n">
+        <v>0</v>
+      </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>0</v>
+      </c>
+      <c r="R429" t="n">
+        <v>0</v>
+      </c>
+      <c r="S429" t="n">
+        <v>0</v>
+      </c>
+      <c r="T429" t="n">
+        <v>0</v>
+      </c>
+      <c r="U429" t="n">
+        <v>0</v>
+      </c>
+      <c r="V429" t="n">
+        <v>0</v>
+      </c>
+      <c r="W429" t="n">
+        <v>0</v>
+      </c>
+      <c r="X429" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:32.805644</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Thimphu City - Tensung</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>7-1</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>90</v>
+      </c>
+      <c r="E430" t="n">
+        <v>8</v>
+      </c>
+      <c r="F430" t="n">
+        <v>0</v>
+      </c>
+      <c r="G430" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" t="n">
+        <v>7</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="n">
+        <v>0</v>
+      </c>
+      <c r="M430" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" t="n">
+        <v>1</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>0</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0</v>
+      </c>
+      <c r="S430" t="n">
+        <v>0</v>
+      </c>
+      <c r="T430" t="n">
+        <v>0</v>
+      </c>
+      <c r="U430" t="n">
+        <v>0</v>
+      </c>
+      <c r="V430" t="n">
+        <v>0</v>
+      </c>
+      <c r="W430" t="n">
+        <v>0</v>
+      </c>
+      <c r="X430" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:34.812226</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Estrela - Lusitano Évora 1911</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
+      <c r="F431" t="n">
+        <v>0</v>
+      </c>
+      <c r="G431" t="n">
+        <v>0</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0</v>
+      </c>
+      <c r="I431" t="n">
+        <v>0</v>
+      </c>
+      <c r="J431" t="n">
+        <v>0</v>
+      </c>
+      <c r="K431" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" t="n">
+        <v>0</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>0</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0</v>
+      </c>
+      <c r="S431" t="n">
+        <v>0</v>
+      </c>
+      <c r="T431" t="n">
+        <v>0</v>
+      </c>
+      <c r="U431" t="n">
+        <v>0</v>
+      </c>
+      <c r="V431" t="n">
+        <v>0</v>
+      </c>
+      <c r="W431" t="n">
+        <v>0</v>
+      </c>
+      <c r="X431" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:32:37.298444</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Persebaya Surabaya - PSMS Medan</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>90</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G432" t="n">
+        <v>0</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>5</v>
+      </c>
+      <c r="J432" t="n">
+        <v>1</v>
+      </c>
+      <c r="K432" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="n">
+        <v>2</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
+        <v>3</v>
+      </c>
+      <c r="T432" t="n">
+        <v>0</v>
+      </c>
+      <c r="U432" t="n">
+        <v>0</v>
+      </c>
+      <c r="V432" t="n">
+        <v>0</v>
+      </c>
+      <c r="W432" t="n">
+        <v>0</v>
+      </c>
+      <c r="X432" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:20:32.809859</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Fredrikstad FK U19 - Stabæk U19</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>90</v>
+      </c>
+      <c r="E433" t="n">
+        <v>3</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0</v>
+      </c>
+      <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>1</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>0</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
+      <c r="T433" t="n">
+        <v>0</v>
+      </c>
+      <c r="U433" t="n">
+        <v>0</v>
+      </c>
+      <c r="V433" t="n">
+        <v>0</v>
+      </c>
+      <c r="W433" t="n">
+        <v>0</v>
+      </c>
+      <c r="X433" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:20:53.428296</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>KVC Westerlo - Kifisia</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>90</v>
+      </c>
+      <c r="E434" t="n">
+        <v>2</v>
+      </c>
+      <c r="F434" t="n">
+        <v>0</v>
+      </c>
+      <c r="G434" t="n">
+        <v>0</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="n">
+        <v>1</v>
+      </c>
+      <c r="K434" t="n">
+        <v>0</v>
+      </c>
+      <c r="L434" t="n">
+        <v>0</v>
+      </c>
+      <c r="M434" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>1</v>
+      </c>
+      <c r="P434" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>0</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0</v>
+      </c>
+      <c r="S434" t="n">
+        <v>0</v>
+      </c>
+      <c r="T434" t="n">
+        <v>0</v>
+      </c>
+      <c r="U434" t="n">
+        <v>0</v>
+      </c>
+      <c r="V434" t="n">
+        <v>0</v>
+      </c>
+      <c r="W434" t="n">
+        <v>0</v>
+      </c>
+      <c r="X434" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:21:13.921939</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>KVZ - Al Hilal Omdurman</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>90</v>
+      </c>
+      <c r="E435" t="n">
+        <v>4</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>4</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>0</v>
+      </c>
+      <c r="R435" t="n">
+        <v>0</v>
+      </c>
+      <c r="S435" t="n">
+        <v>0</v>
+      </c>
+      <c r="T435" t="n">
+        <v>0</v>
+      </c>
+      <c r="U435" t="n">
+        <v>0</v>
+      </c>
+      <c r="V435" t="n">
+        <v>0</v>
+      </c>
+      <c r="W435" t="n">
+        <v>0</v>
+      </c>
+      <c r="X435" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:21:35.617876</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen - Genk</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>90</v>
+      </c>
+      <c r="E436" t="n">
+        <v>4</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="n">
+        <v>4</v>
+      </c>
+      <c r="K436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>0</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0</v>
+      </c>
+      <c r="S436" t="n">
+        <v>0</v>
+      </c>
+      <c r="T436" t="n">
+        <v>0</v>
+      </c>
+      <c r="U436" t="n">
+        <v>0</v>
+      </c>
+      <c r="V436" t="n">
+        <v>0</v>
+      </c>
+      <c r="W436" t="n">
+        <v>0</v>
+      </c>
+      <c r="X436" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:21:56.917900</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Reyady Abaseya - Tadamon Sour</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>90</v>
+      </c>
+      <c r="E437" t="n">
+        <v>3</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>2</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="n">
+        <v>0</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>1</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0</v>
+      </c>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0</v>
+      </c>
+      <c r="V437" t="n">
+        <v>0</v>
+      </c>
+      <c r="W437" t="n">
+        <v>0</v>
+      </c>
+      <c r="X437" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:22:14.681931</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Ilpar - Metallurg Asha</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>90</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>0</v>
+      </c>
+      <c r="U438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V438" t="n">
+        <v>0</v>
+      </c>
+      <c r="W438" t="n">
+        <v>0</v>
+      </c>
+      <c r="X438" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:22:36.532089</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Lecce - Bistrica</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>90</v>
+      </c>
+      <c r="E439" t="n">
+        <v>7</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" t="n">
+        <v>5</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>2</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="n">
+        <v>0</v>
+      </c>
+      <c r="V439" t="n">
+        <v>0</v>
+      </c>
+      <c r="W439" t="n">
+        <v>0</v>
+      </c>
+      <c r="X439" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:23:00.000530</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Dukagjini - FC Lugano</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>90</v>
+      </c>
+      <c r="E440" t="n">
+        <v>6</v>
+      </c>
+      <c r="F440" t="n">
+        <v>6</v>
+      </c>
+      <c r="G440" t="n">
+        <v>21</v>
+      </c>
+      <c r="H440" t="n">
+        <v>11</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="n">
+        <v>1</v>
+      </c>
+      <c r="L440" t="n">
+        <v>9</v>
+      </c>
+      <c r="M440" t="n">
+        <v>4</v>
+      </c>
+      <c r="N440" t="n">
+        <v>0</v>
+      </c>
+      <c r="O440" t="n">
+        <v>5</v>
+      </c>
+      <c r="P440" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>12</v>
+      </c>
+      <c r="R440" t="n">
+        <v>7</v>
+      </c>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="n">
+        <v>0</v>
+      </c>
+      <c r="V440" t="n">
+        <v>0</v>
+      </c>
+      <c r="W440" t="n">
+        <v>0</v>
+      </c>
+      <c r="X440" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:23:21.530442</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Kristall - Znamya Noginsk</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>90</v>
+      </c>
+      <c r="E441" t="n">
+        <v>5</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0</v>
+      </c>
+      <c r="M441" t="n">
+        <v>0</v>
+      </c>
+      <c r="N441" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>3</v>
+      </c>
+      <c r="P441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>0</v>
+      </c>
+      <c r="R441" t="n">
+        <v>0</v>
+      </c>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="n">
+        <v>0</v>
+      </c>
+      <c r="V441" t="n">
+        <v>0</v>
+      </c>
+      <c r="W441" t="n">
+        <v>0</v>
+      </c>
+      <c r="X441" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:23:46.006573</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Frosinone - Sambenedettese</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>90</v>
+      </c>
+      <c r="E442" t="n">
+        <v>2</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0</v>
+      </c>
+      <c r="G442" t="n">
+        <v>0</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="n">
+        <v>0</v>
+      </c>
+      <c r="L442" t="n">
+        <v>0</v>
+      </c>
+      <c r="M442" t="n">
+        <v>0</v>
+      </c>
+      <c r="N442" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>1</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0</v>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
+      <c r="V442" t="n">
+        <v>0</v>
+      </c>
+      <c r="W442" t="n">
+        <v>0</v>
+      </c>
+      <c r="X442" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:24:11.996966</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Aerostar Bacau - CSM FC Vaslui</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="n">
+        <v>0</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="n">
+        <v>0</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" t="n">
+        <v>0</v>
+      </c>
+      <c r="L443" t="n">
+        <v>0</v>
+      </c>
+      <c r="M443" t="n">
+        <v>0</v>
+      </c>
+      <c r="N443" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>0</v>
+      </c>
+      <c r="R443" t="n">
+        <v>0</v>
+      </c>
+      <c r="S443" t="n">
+        <v>0</v>
+      </c>
+      <c r="T443" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V443" t="n">
+        <v>0</v>
+      </c>
+      <c r="W443" t="n">
+        <v>0</v>
+      </c>
+      <c r="X443" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:24:34.489407</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Agigea - Axiopolis</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>90</v>
+      </c>
+      <c r="E444" t="n">
+        <v>5</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="n">
+        <v>0</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="n">
+        <v>2</v>
+      </c>
+      <c r="K444" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0</v>
+      </c>
+      <c r="M444" t="n">
+        <v>0</v>
+      </c>
+      <c r="N444" t="n">
+        <v>0</v>
+      </c>
+      <c r="O444" t="n">
+        <v>3</v>
+      </c>
+      <c r="P444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>0</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0</v>
+      </c>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0</v>
+      </c>
+      <c r="V444" t="n">
+        <v>0</v>
+      </c>
+      <c r="W444" t="n">
+        <v>0</v>
+      </c>
+      <c r="X444" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:24:54.370424</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Berca - Valenii de Munte</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>90</v>
+      </c>
+      <c r="E445" t="n">
+        <v>7</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="n">
+        <v>0</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="n">
+        <v>5</v>
+      </c>
+      <c r="K445" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" t="n">
+        <v>0</v>
+      </c>
+      <c r="M445" t="n">
+        <v>0</v>
+      </c>
+      <c r="N445" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>2</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>0</v>
+      </c>
+      <c r="R445" t="n">
+        <v>0</v>
+      </c>
+      <c r="S445" t="n">
+        <v>0</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="n">
+        <v>0</v>
+      </c>
+      <c r="V445" t="n">
+        <v>0</v>
+      </c>
+      <c r="W445" t="n">
+        <v>0</v>
+      </c>
+      <c r="X445" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:15.572831</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Bihorul Beiuş - Sânmartin</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>90</v>
+      </c>
+      <c r="E446" t="n">
+        <v>1</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" t="n">
+        <v>0</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>1</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0</v>
+      </c>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0</v>
+      </c>
+      <c r="V446" t="n">
+        <v>0</v>
+      </c>
+      <c r="W446" t="n">
+        <v>0</v>
+      </c>
+      <c r="X446" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:31.234559</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Bolintin Vale - Axi Adunații-Copăceni</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>0</v>
+      </c>
+      <c r="E447" t="n">
+        <v>0</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G447" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" t="n">
+        <v>0</v>
+      </c>
+      <c r="M447" t="n">
+        <v>0</v>
+      </c>
+      <c r="N447" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>0</v>
+      </c>
+      <c r="R447" t="n">
+        <v>0</v>
+      </c>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="n">
+        <v>0</v>
+      </c>
+      <c r="V447" t="n">
+        <v>0</v>
+      </c>
+      <c r="W447" t="n">
+        <v>0</v>
+      </c>
+      <c r="X447" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:49.741113</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Bradul Putna - Bucovina Rădăuţi</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>9-0</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>90</v>
+      </c>
+      <c r="E448" t="n">
+        <v>9</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="n">
+        <v>9</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L448" t="n">
+        <v>0</v>
+      </c>
+      <c r="M448" t="n">
+        <v>0</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="P448" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>0</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0</v>
+      </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
+      <c r="T448" t="n">
+        <v>0</v>
+      </c>
+      <c r="U448" t="n">
+        <v>0</v>
+      </c>
+      <c r="V448" t="n">
+        <v>0</v>
+      </c>
+      <c r="W448" t="n">
+        <v>0</v>
+      </c>
+      <c r="X448" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:07.275237</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Caransebes - Ghiroda şi Giarmata Vii</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>90</v>
+      </c>
+      <c r="E449" t="n">
+        <v>3</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" t="n">
+        <v>0</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="n">
+        <v>2</v>
+      </c>
+      <c r="K449" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" t="n">
+        <v>0</v>
+      </c>
+      <c r="M449" t="n">
+        <v>0</v>
+      </c>
+      <c r="N449" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>1</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0</v>
+      </c>
+      <c r="S449" t="n">
+        <v>0</v>
+      </c>
+      <c r="T449" t="n">
+        <v>0</v>
+      </c>
+      <c r="U449" t="n">
+        <v>0</v>
+      </c>
+      <c r="V449" t="n">
+        <v>0</v>
+      </c>
+      <c r="W449" t="n">
+        <v>0</v>
+      </c>
+      <c r="X449" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:24.379576</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Chiesd - Sighetu Marmaţiei</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>90</v>
+      </c>
+      <c r="E450" t="n">
+        <v>5</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="n">
+        <v>0</v>
+      </c>
+      <c r="L450" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" t="n">
+        <v>0</v>
+      </c>
+      <c r="N450" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>4</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>0</v>
+      </c>
+      <c r="R450" t="n">
+        <v>0</v>
+      </c>
+      <c r="S450" t="n">
+        <v>0</v>
+      </c>
+      <c r="T450" t="n">
+        <v>0</v>
+      </c>
+      <c r="U450" t="n">
+        <v>0</v>
+      </c>
+      <c r="V450" t="n">
+        <v>0</v>
+      </c>
+      <c r="W450" t="n">
+        <v>0</v>
+      </c>
+      <c r="X450" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:45.917599</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Corona Braşov - ARO Muscelul Câmpulung</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>0</v>
+      </c>
+      <c r="E451" t="n">
+        <v>0</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G451" t="n">
+        <v>0</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" t="n">
+        <v>0</v>
+      </c>
+      <c r="L451" t="n">
+        <v>0</v>
+      </c>
+      <c r="M451" t="n">
+        <v>0</v>
+      </c>
+      <c r="N451" t="n">
+        <v>0</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>0</v>
+      </c>
+      <c r="R451" t="n">
+        <v>0</v>
+      </c>
+      <c r="S451" t="n">
+        <v>0</v>
+      </c>
+      <c r="T451" t="n">
+        <v>0</v>
+      </c>
+      <c r="U451" t="n">
+        <v>0</v>
+      </c>
+      <c r="V451" t="n">
+        <v>0</v>
+      </c>
+      <c r="W451" t="n">
+        <v>0</v>
+      </c>
+      <c r="X451" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:27:07.663815</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Râmnicu Sărat - CSM Adjud</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>90</v>
+      </c>
+      <c r="E452" t="n">
+        <v>3</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" t="n">
+        <v>0</v>
+      </c>
+      <c r="K452" t="n">
+        <v>0</v>
+      </c>
+      <c r="L452" t="n">
+        <v>0</v>
+      </c>
+      <c r="M452" t="n">
+        <v>0</v>
+      </c>
+      <c r="N452" t="n">
+        <v>0</v>
+      </c>
+      <c r="O452" t="n">
+        <v>3</v>
+      </c>
+      <c r="P452" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>0</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0</v>
+      </c>
+      <c r="S452" t="n">
+        <v>0</v>
+      </c>
+      <c r="T452" t="n">
+        <v>0</v>
+      </c>
+      <c r="U452" t="n">
+        <v>0</v>
+      </c>
+      <c r="V452" t="n">
+        <v>0</v>
+      </c>
+      <c r="W452" t="n">
+        <v>0</v>
+      </c>
+      <c r="X452" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:27:27.919118</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Săcele - Kids Tâmpa Braşov</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>0</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" t="n">
+        <v>0</v>
+      </c>
+      <c r="L453" t="n">
+        <v>0</v>
+      </c>
+      <c r="M453" t="n">
+        <v>0</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+      <c r="P453" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>0</v>
+      </c>
+      <c r="R453" t="n">
+        <v>0</v>
+      </c>
+      <c r="S453" t="n">
+        <v>0</v>
+      </c>
+      <c r="T453" t="n">
+        <v>0</v>
+      </c>
+      <c r="U453" t="n">
+        <v>0</v>
+      </c>
+      <c r="V453" t="n">
+        <v>0</v>
+      </c>
+      <c r="W453" t="n">
+        <v>0</v>
+      </c>
+      <c r="X453" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:27:48.726490</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>CSM Targu Jiu - Vulturii Fărcăşeşti</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>90</v>
+      </c>
+      <c r="E454" t="n">
+        <v>5</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" t="n">
+        <v>3</v>
+      </c>
+      <c r="K454" t="n">
+        <v>0</v>
+      </c>
+      <c r="L454" t="n">
+        <v>0</v>
+      </c>
+      <c r="M454" t="n">
+        <v>0</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" t="n">
+        <v>2</v>
+      </c>
+      <c r="P454" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>0</v>
+      </c>
+      <c r="R454" t="n">
+        <v>0</v>
+      </c>
+      <c r="S454" t="n">
+        <v>0</v>
+      </c>
+      <c r="T454" t="n">
+        <v>0</v>
+      </c>
+      <c r="U454" t="n">
+        <v>0</v>
+      </c>
+      <c r="V454" t="n">
+        <v>0</v>
+      </c>
+      <c r="W454" t="n">
+        <v>0</v>
+      </c>
+      <c r="X454" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:28:11.397648</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Plopeni - Baicoi</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>90</v>
+      </c>
+      <c r="E455" t="n">
+        <v>3</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0</v>
+      </c>
+      <c r="I455" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" t="n">
+        <v>1</v>
+      </c>
+      <c r="K455" t="n">
+        <v>0</v>
+      </c>
+      <c r="L455" t="n">
+        <v>0</v>
+      </c>
+      <c r="M455" t="n">
+        <v>0</v>
+      </c>
+      <c r="N455" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" t="n">
+        <v>2</v>
+      </c>
+      <c r="P455" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>0</v>
+      </c>
+      <c r="R455" t="n">
+        <v>0</v>
+      </c>
+      <c r="S455" t="n">
+        <v>0</v>
+      </c>
+      <c r="T455" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" t="n">
+        <v>0</v>
+      </c>
+      <c r="V455" t="n">
+        <v>0</v>
+      </c>
+      <c r="W455" t="n">
+        <v>0</v>
+      </c>
+      <c r="X455" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:28:33.119394</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Oltul Curtişoara - Academica Balș</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" t="n">
+        <v>0</v>
+      </c>
+      <c r="L456" t="n">
+        <v>0</v>
+      </c>
+      <c r="M456" t="n">
+        <v>0</v>
+      </c>
+      <c r="N456" t="n">
+        <v>0</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>0</v>
+      </c>
+      <c r="R456" t="n">
+        <v>0</v>
+      </c>
+      <c r="S456" t="n">
+        <v>0</v>
+      </c>
+      <c r="T456" t="n">
+        <v>0</v>
+      </c>
+      <c r="U456" t="n">
+        <v>0</v>
+      </c>
+      <c r="V456" t="n">
+        <v>0</v>
+      </c>
+      <c r="W456" t="n">
+        <v>0</v>
+      </c>
+      <c r="X456" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:28:50.179950</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Domnesti IF - Unirea Bascov</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>90</v>
+      </c>
+      <c r="E457" t="n">
+        <v>5</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0</v>
+      </c>
+      <c r="I457" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" t="n">
+        <v>3</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0</v>
+      </c>
+      <c r="L457" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" t="n">
+        <v>0</v>
+      </c>
+      <c r="N457" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" t="n">
+        <v>2</v>
+      </c>
+      <c r="P457" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>0</v>
+      </c>
+      <c r="R457" t="n">
+        <v>0</v>
+      </c>
+      <c r="S457" t="n">
+        <v>0</v>
+      </c>
+      <c r="T457" t="n">
+        <v>0</v>
+      </c>
+      <c r="U457" t="n">
+        <v>0</v>
+      </c>
+      <c r="V457" t="n">
+        <v>0</v>
+      </c>
+      <c r="W457" t="n">
+        <v>0</v>
+      </c>
+      <c r="X457" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:29:13.362177</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Dunărea 2020 Giurgiu - Alexandria</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>90</v>
+      </c>
+      <c r="E458" t="n">
+        <v>3</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" t="n">
+        <v>0</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="n">
+        <v>3</v>
+      </c>
+      <c r="K458" t="n">
+        <v>0</v>
+      </c>
+      <c r="L458" t="n">
+        <v>0</v>
+      </c>
+      <c r="M458" t="n">
+        <v>0</v>
+      </c>
+      <c r="N458" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+      <c r="P458" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>0</v>
+      </c>
+      <c r="R458" t="n">
+        <v>0</v>
+      </c>
+      <c r="S458" t="n">
+        <v>0</v>
+      </c>
+      <c r="T458" t="n">
+        <v>0</v>
+      </c>
+      <c r="U458" t="n">
+        <v>0</v>
+      </c>
+      <c r="V458" t="n">
+        <v>0</v>
+      </c>
+      <c r="W458" t="n">
+        <v>0</v>
+      </c>
+      <c r="X458" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:29:37.916836</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Pucioasa - Tricolorul Breaza</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>90</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0</v>
+      </c>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>0</v>
+      </c>
+      <c r="R459" t="n">
+        <v>0</v>
+      </c>
+      <c r="S459" t="n">
+        <v>0</v>
+      </c>
+      <c r="T459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="n">
+        <v>0</v>
+      </c>
+      <c r="V459" t="n">
+        <v>0</v>
+      </c>
+      <c r="W459" t="n">
+        <v>0</v>
+      </c>
+      <c r="X459" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:30:00.518548</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Gilortul - Păușești</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>0</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>0</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" t="n">
+        <v>0</v>
+      </c>
+      <c r="M460" t="n">
+        <v>0</v>
+      </c>
+      <c r="N460" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+      <c r="P460" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>0</v>
+      </c>
+      <c r="R460" t="n">
+        <v>0</v>
+      </c>
+      <c r="S460" t="n">
+        <v>0</v>
+      </c>
+      <c r="T460" t="n">
+        <v>0</v>
+      </c>
+      <c r="U460" t="n">
+        <v>0</v>
+      </c>
+      <c r="V460" t="n">
+        <v>0</v>
+      </c>
+      <c r="W460" t="n">
+        <v>0</v>
+      </c>
+      <c r="X460" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:31:43.348587</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2 de Mayo - Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>90</v>
+      </c>
+      <c r="E461" t="n">
+        <v>3</v>
+      </c>
+      <c r="F461" t="n">
+        <v>6</v>
+      </c>
+      <c r="G461" t="n">
+        <v>28</v>
+      </c>
+      <c r="H461" t="n">
+        <v>13</v>
+      </c>
+      <c r="I461" t="n">
+        <v>2</v>
+      </c>
+      <c r="J461" t="n">
+        <v>2</v>
+      </c>
+      <c r="K461" t="n">
+        <v>4</v>
+      </c>
+      <c r="L461" t="n">
+        <v>11</v>
+      </c>
+      <c r="M461" t="n">
+        <v>4</v>
+      </c>
+      <c r="N461" t="n">
+        <v>1</v>
+      </c>
+      <c r="O461" t="n">
+        <v>1</v>
+      </c>
+      <c r="P461" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>17</v>
+      </c>
+      <c r="R461" t="n">
+        <v>9</v>
+      </c>
+      <c r="S461" t="n">
+        <v>1</v>
+      </c>
+      <c r="T461" t="n">
+        <v>0</v>
+      </c>
+      <c r="U461" t="n">
+        <v>0</v>
+      </c>
+      <c r="V461" t="n">
+        <v>0</v>
+      </c>
+      <c r="W461" t="n">
+        <v>0</v>
+      </c>
+      <c r="X461" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:32:01.746375</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Cacahuatique - Atletico Balboa</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>90</v>
+      </c>
+      <c r="E462" t="n">
+        <v>6</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0</v>
+      </c>
+      <c r="G462" t="n">
+        <v>0</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0</v>
+      </c>
+      <c r="J462" t="n">
+        <v>4</v>
+      </c>
+      <c r="K462" t="n">
+        <v>0</v>
+      </c>
+      <c r="L462" t="n">
+        <v>0</v>
+      </c>
+      <c r="M462" t="n">
+        <v>0</v>
+      </c>
+      <c r="N462" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" t="n">
+        <v>2</v>
+      </c>
+      <c r="P462" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>0</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0</v>
+      </c>
+      <c r="S462" t="n">
+        <v>0</v>
+      </c>
+      <c r="T462" t="n">
+        <v>0</v>
+      </c>
+      <c r="U462" t="n">
+        <v>0</v>
+      </c>
+      <c r="V462" t="n">
+        <v>0</v>
+      </c>
+      <c r="W462" t="n">
+        <v>0</v>
+      </c>
+      <c r="X462" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:32:24.840164</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Banfield - Sarmiento Junin</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>90</v>
+      </c>
+      <c r="E463" t="n">
+        <v>5</v>
+      </c>
+      <c r="F463" t="n">
+        <v>7</v>
+      </c>
+      <c r="G463" t="n">
+        <v>29</v>
+      </c>
+      <c r="H463" t="n">
+        <v>13</v>
+      </c>
+      <c r="I463" t="n">
+        <v>1</v>
+      </c>
+      <c r="J463" t="n">
+        <v>3</v>
+      </c>
+      <c r="K463" t="n">
+        <v>3</v>
+      </c>
+      <c r="L463" t="n">
+        <v>16</v>
+      </c>
+      <c r="M463" t="n">
+        <v>8</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0</v>
+      </c>
+      <c r="O463" t="n">
+        <v>2</v>
+      </c>
+      <c r="P463" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>13</v>
+      </c>
+      <c r="R463" t="n">
+        <v>5</v>
+      </c>
+      <c r="S463" t="n">
+        <v>1</v>
+      </c>
+      <c r="T463" t="n">
+        <v>0</v>
+      </c>
+      <c r="U463" t="n">
+        <v>0</v>
+      </c>
+      <c r="V463" t="n">
+        <v>0</v>
+      </c>
+      <c r="W463" t="n">
+        <v>0</v>
+      </c>
+      <c r="X463" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:32:46.431928</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>San Lorenzo - Gimnasia M.</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>90</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1</v>
+      </c>
+      <c r="F464" t="n">
+        <v>9</v>
+      </c>
+      <c r="G464" t="n">
+        <v>26</v>
+      </c>
+      <c r="H464" t="n">
+        <v>8</v>
+      </c>
+      <c r="I464" t="n">
+        <v>4</v>
+      </c>
+      <c r="J464" t="n">
+        <v>1</v>
+      </c>
+      <c r="K464" t="n">
+        <v>4</v>
+      </c>
+      <c r="L464" t="n">
+        <v>13</v>
+      </c>
+      <c r="M464" t="n">
+        <v>5</v>
+      </c>
+      <c r="N464" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>13</v>
+      </c>
+      <c r="R464" t="n">
+        <v>3</v>
+      </c>
+      <c r="S464" t="n">
+        <v>4</v>
+      </c>
+      <c r="T464" t="n">
+        <v>0</v>
+      </c>
+      <c r="U464" t="n">
+        <v>0</v>
+      </c>
+      <c r="V464" t="n">
+        <v>0</v>
+      </c>
+      <c r="W464" t="n">
+        <v>0</v>
+      </c>
+      <c r="X464" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:33:10.571535</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Tigre - Club Nacional</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>90</v>
+      </c>
+      <c r="E465" t="n">
+        <v>3</v>
+      </c>
+      <c r="F465" t="n">
+        <v>8</v>
+      </c>
+      <c r="G465" t="n">
+        <v>16</v>
+      </c>
+      <c r="H465" t="n">
+        <v>6</v>
+      </c>
+      <c r="I465" t="n">
+        <v>7</v>
+      </c>
+      <c r="J465" t="n">
+        <v>1</v>
+      </c>
+      <c r="K465" t="n">
+        <v>2</v>
+      </c>
+      <c r="L465" t="n">
+        <v>9</v>
+      </c>
+      <c r="M465" t="n">
+        <v>3</v>
+      </c>
+      <c r="N465" t="n">
+        <v>3</v>
+      </c>
+      <c r="O465" t="n">
+        <v>2</v>
+      </c>
+      <c r="P465" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>7</v>
+      </c>
+      <c r="R465" t="n">
+        <v>3</v>
+      </c>
+      <c r="S465" t="n">
+        <v>4</v>
+      </c>
+      <c r="T465" t="n">
+        <v>0</v>
+      </c>
+      <c r="U465" t="n">
+        <v>0</v>
+      </c>
+      <c r="V465" t="n">
+        <v>0</v>
+      </c>
+      <c r="W465" t="n">
+        <v>0</v>
+      </c>
+      <c r="X465" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:33:32.322843</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Juventude - Avai</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>90</v>
+      </c>
+      <c r="E466" t="n">
+        <v>1</v>
+      </c>
+      <c r="F466" t="n">
+        <v>6</v>
+      </c>
+      <c r="G466" t="n">
+        <v>19</v>
+      </c>
+      <c r="H466" t="n">
+        <v>6</v>
+      </c>
+      <c r="I466" t="n">
+        <v>3</v>
+      </c>
+      <c r="J466" t="n">
+        <v>1</v>
+      </c>
+      <c r="K466" t="n">
+        <v>3</v>
+      </c>
+      <c r="L466" t="n">
+        <v>11</v>
+      </c>
+      <c r="M466" t="n">
+        <v>6</v>
+      </c>
+      <c r="N466" t="n">
+        <v>1</v>
+      </c>
+      <c r="O466" t="n">
+        <v>0</v>
+      </c>
+      <c r="P466" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>8</v>
+      </c>
+      <c r="R466" t="n">
+        <v>0</v>
+      </c>
+      <c r="S466" t="n">
+        <v>2</v>
+      </c>
+      <c r="T466" t="n">
+        <v>0</v>
+      </c>
+      <c r="U466" t="n">
+        <v>0</v>
+      </c>
+      <c r="V466" t="n">
+        <v>0</v>
+      </c>
+      <c r="W466" t="n">
+        <v>0</v>
+      </c>
+      <c r="X466" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:33:53.787575</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Ponte Preta - Athletic Club</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>90</v>
+      </c>
+      <c r="E467" t="n">
+        <v>2</v>
+      </c>
+      <c r="F467" t="n">
+        <v>2</v>
+      </c>
+      <c r="G467" t="n">
+        <v>26</v>
+      </c>
+      <c r="H467" t="n">
+        <v>10</v>
+      </c>
+      <c r="I467" t="n">
+        <v>9</v>
+      </c>
+      <c r="J467" t="n">
+        <v>1</v>
+      </c>
+      <c r="K467" t="n">
+        <v>1</v>
+      </c>
+      <c r="L467" t="n">
+        <v>14</v>
+      </c>
+      <c r="M467" t="n">
+        <v>6</v>
+      </c>
+      <c r="N467" t="n">
+        <v>4</v>
+      </c>
+      <c r="O467" t="n">
+        <v>1</v>
+      </c>
+      <c r="P467" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>12</v>
+      </c>
+      <c r="R467" t="n">
+        <v>4</v>
+      </c>
+      <c r="S467" t="n">
+        <v>5</v>
+      </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="n">
+        <v>0</v>
+      </c>
+      <c r="V467" t="n">
+        <v>0</v>
+      </c>
+      <c r="W467" t="n">
+        <v>0</v>
+      </c>
+      <c r="X467" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:34:16.326401</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Independiente F.b.c. - Deportivo Capiata</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>90</v>
+      </c>
+      <c r="E468" t="n">
+        <v>2</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+      <c r="J468" t="n">
+        <v>1</v>
+      </c>
+      <c r="K468" t="n">
+        <v>0</v>
+      </c>
+      <c r="L468" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" t="n">
+        <v>0</v>
+      </c>
+      <c r="N468" t="n">
+        <v>0</v>
+      </c>
+      <c r="O468" t="n">
+        <v>1</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>0</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0</v>
+      </c>
+      <c r="S468" t="n">
+        <v>0</v>
+      </c>
+      <c r="T468" t="n">
+        <v>0</v>
+      </c>
+      <c r="U468" t="n">
+        <v>0</v>
+      </c>
+      <c r="V468" t="n">
+        <v>0</v>
+      </c>
+      <c r="W468" t="n">
+        <v>0</v>
+      </c>
+      <c r="X468" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:34:38.409079</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>AFC Toronto W - Calgary Wild W</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>0</v>
+      </c>
+      <c r="E469" t="n">
+        <v>0</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+      <c r="J469" t="n">
+        <v>0</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" t="n">
+        <v>0</v>
+      </c>
+      <c r="M469" t="n">
+        <v>0</v>
+      </c>
+      <c r="N469" t="n">
+        <v>0</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>0</v>
+      </c>
+      <c r="R469" t="n">
+        <v>0</v>
+      </c>
+      <c r="S469" t="n">
+        <v>0</v>
+      </c>
+      <c r="T469" t="n">
+        <v>0</v>
+      </c>
+      <c r="U469" t="n">
+        <v>0</v>
+      </c>
+      <c r="V469" t="n">
+        <v>0</v>
+      </c>
+      <c r="W469" t="n">
+        <v>0</v>
+      </c>
+      <c r="X469" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:35:01.072298</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Quindio - Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>120</v>
+      </c>
+      <c r="E470" t="n">
+        <v>3</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0</v>
+      </c>
+      <c r="G470" t="n">
+        <v>0</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="n">
+        <v>2</v>
+      </c>
+      <c r="K470" t="n">
+        <v>0</v>
+      </c>
+      <c r="L470" t="n">
+        <v>0</v>
+      </c>
+      <c r="M470" t="n">
+        <v>0</v>
+      </c>
+      <c r="N470" t="n">
+        <v>0</v>
+      </c>
+      <c r="O470" t="n">
+        <v>1</v>
+      </c>
+      <c r="P470" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>0</v>
+      </c>
+      <c r="R470" t="n">
+        <v>0</v>
+      </c>
+      <c r="S470" t="n">
+        <v>0</v>
+      </c>
+      <c r="T470" t="n">
+        <v>0</v>
+      </c>
+      <c r="U470" t="n">
+        <v>0</v>
+      </c>
+      <c r="V470" t="n">
+        <v>0</v>
+      </c>
+      <c r="W470" t="n">
+        <v>0</v>
+      </c>
+      <c r="X470" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:35:24.330550</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Bogota FC - Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>90</v>
+      </c>
+      <c r="E471" t="n">
+        <v>3</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0</v>
+      </c>
+      <c r="O471" t="n">
+        <v>3</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>0</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0</v>
+      </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
+      <c r="T471" t="n">
+        <v>0</v>
+      </c>
+      <c r="U471" t="n">
+        <v>0</v>
+      </c>
+      <c r="V471" t="n">
+        <v>0</v>
+      </c>
+      <c r="W471" t="n">
+        <v>0</v>
+      </c>
+      <c r="X471" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:35:45.151238</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Verdes - CD Motagua</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>90</v>
+      </c>
+      <c r="E472" t="n">
+        <v>5</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0</v>
+      </c>
+      <c r="H472" t="n">
+        <v>0</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" t="n">
+        <v>0</v>
+      </c>
+      <c r="K472" t="n">
+        <v>0</v>
+      </c>
+      <c r="L472" t="n">
+        <v>0</v>
+      </c>
+      <c r="M472" t="n">
+        <v>0</v>
+      </c>
+      <c r="N472" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" t="n">
+        <v>5</v>
+      </c>
+      <c r="P472" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>0</v>
+      </c>
+      <c r="R472" t="n">
+        <v>0</v>
+      </c>
+      <c r="S472" t="n">
+        <v>0</v>
+      </c>
+      <c r="T472" t="n">
+        <v>0</v>
+      </c>
+      <c r="U472" t="n">
+        <v>0</v>
+      </c>
+      <c r="V472" t="n">
+        <v>0</v>
+      </c>
+      <c r="W472" t="n">
+        <v>0</v>
+      </c>
+      <c r="X472" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:36:17.231030</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Argentinos JRS - Estudiantes de Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>90</v>
+      </c>
+      <c r="E473" t="n">
+        <v>3</v>
+      </c>
+      <c r="F473" t="n">
+        <v>10</v>
+      </c>
+      <c r="G473" t="n">
+        <v>29</v>
+      </c>
+      <c r="H473" t="n">
+        <v>13</v>
+      </c>
+      <c r="I473" t="n">
+        <v>1</v>
+      </c>
+      <c r="J473" t="n">
+        <v>3</v>
+      </c>
+      <c r="K473" t="n">
+        <v>6</v>
+      </c>
+      <c r="L473" t="n">
+        <v>17</v>
+      </c>
+      <c r="M473" t="n">
+        <v>9</v>
+      </c>
+      <c r="N473" t="n">
+        <v>0</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>12</v>
+      </c>
+      <c r="R473" t="n">
+        <v>4</v>
+      </c>
+      <c r="S473" t="n">
+        <v>1</v>
+      </c>
+      <c r="T473" t="n">
+        <v>0</v>
+      </c>
+      <c r="U473" t="n">
+        <v>0</v>
+      </c>
+      <c r="V473" t="n">
+        <v>0</v>
+      </c>
+      <c r="W473" t="n">
+        <v>0</v>
+      </c>
+      <c r="X473" t="n">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals.xlsx
+++ b/data/signals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X473"/>
+  <dimension ref="A1:X531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38298,6 +38298,4646 @@
         <v>29</v>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:04.742453</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Boca Juniors - Estudiantes L.P.</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>90</v>
+      </c>
+      <c r="E474" t="n">
+        <v>1</v>
+      </c>
+      <c r="F474" t="n">
+        <v>7</v>
+      </c>
+      <c r="G474" t="n">
+        <v>20</v>
+      </c>
+      <c r="H474" t="n">
+        <v>6</v>
+      </c>
+      <c r="I474" t="n">
+        <v>4</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1</v>
+      </c>
+      <c r="K474" t="n">
+        <v>5</v>
+      </c>
+      <c r="L474" t="n">
+        <v>12</v>
+      </c>
+      <c r="M474" t="n">
+        <v>2</v>
+      </c>
+      <c r="N474" t="n">
+        <v>1</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>8</v>
+      </c>
+      <c r="R474" t="n">
+        <v>4</v>
+      </c>
+      <c r="S474" t="n">
+        <v>3</v>
+      </c>
+      <c r="T474" t="n">
+        <v>0</v>
+      </c>
+      <c r="U474" t="n">
+        <v>0</v>
+      </c>
+      <c r="V474" t="n">
+        <v>0</v>
+      </c>
+      <c r="W474" t="n">
+        <v>0</v>
+      </c>
+      <c r="X474" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:12.721508</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Quilmes - Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>90</v>
+      </c>
+      <c r="E475" t="n">
+        <v>2</v>
+      </c>
+      <c r="F475" t="n">
+        <v>9</v>
+      </c>
+      <c r="G475" t="n">
+        <v>12</v>
+      </c>
+      <c r="H475" t="n">
+        <v>5</v>
+      </c>
+      <c r="I475" t="n">
+        <v>4</v>
+      </c>
+      <c r="J475" t="n">
+        <v>2</v>
+      </c>
+      <c r="K475" t="n">
+        <v>7</v>
+      </c>
+      <c r="L475" t="n">
+        <v>12</v>
+      </c>
+      <c r="M475" t="n">
+        <v>5</v>
+      </c>
+      <c r="N475" t="n">
+        <v>2</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="P475" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>0</v>
+      </c>
+      <c r="R475" t="n">
+        <v>0</v>
+      </c>
+      <c r="S475" t="n">
+        <v>2</v>
+      </c>
+      <c r="T475" t="n">
+        <v>0</v>
+      </c>
+      <c r="U475" t="n">
+        <v>0</v>
+      </c>
+      <c r="V475" t="n">
+        <v>0</v>
+      </c>
+      <c r="W475" t="n">
+        <v>0</v>
+      </c>
+      <c r="X475" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:20.828267</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Nacional Potosí - The Strongest</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>90</v>
+      </c>
+      <c r="E476" t="n">
+        <v>5</v>
+      </c>
+      <c r="F476" t="n">
+        <v>0</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="n">
+        <v>2</v>
+      </c>
+      <c r="K476" t="n">
+        <v>0</v>
+      </c>
+      <c r="L476" t="n">
+        <v>0</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0</v>
+      </c>
+      <c r="N476" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" t="n">
+        <v>3</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>0</v>
+      </c>
+      <c r="R476" t="n">
+        <v>0</v>
+      </c>
+      <c r="S476" t="n">
+        <v>0</v>
+      </c>
+      <c r="T476" t="n">
+        <v>0</v>
+      </c>
+      <c r="U476" t="n">
+        <v>0</v>
+      </c>
+      <c r="V476" t="n">
+        <v>0</v>
+      </c>
+      <c r="W476" t="n">
+        <v>0</v>
+      </c>
+      <c r="X476" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:28.808751</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Cruzeiro - Chapecoense-sc</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>90</v>
+      </c>
+      <c r="E477" t="n">
+        <v>2</v>
+      </c>
+      <c r="F477" t="n">
+        <v>14</v>
+      </c>
+      <c r="G477" t="n">
+        <v>31</v>
+      </c>
+      <c r="H477" t="n">
+        <v>11</v>
+      </c>
+      <c r="I477" t="n">
+        <v>6</v>
+      </c>
+      <c r="J477" t="n">
+        <v>2</v>
+      </c>
+      <c r="K477" t="n">
+        <v>12</v>
+      </c>
+      <c r="L477" t="n">
+        <v>29</v>
+      </c>
+      <c r="M477" t="n">
+        <v>11</v>
+      </c>
+      <c r="N477" t="n">
+        <v>2</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
+      <c r="P477" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>2</v>
+      </c>
+      <c r="R477" t="n">
+        <v>0</v>
+      </c>
+      <c r="S477" t="n">
+        <v>4</v>
+      </c>
+      <c r="T477" t="n">
+        <v>0</v>
+      </c>
+      <c r="U477" t="n">
+        <v>0</v>
+      </c>
+      <c r="V477" t="n">
+        <v>0</v>
+      </c>
+      <c r="W477" t="n">
+        <v>0</v>
+      </c>
+      <c r="X477" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:36.963730</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Union San Felipe - Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>90</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1</v>
+      </c>
+      <c r="F478" t="n">
+        <v>8</v>
+      </c>
+      <c r="G478" t="n">
+        <v>18</v>
+      </c>
+      <c r="H478" t="n">
+        <v>5</v>
+      </c>
+      <c r="I478" t="n">
+        <v>3</v>
+      </c>
+      <c r="J478" t="n">
+        <v>0</v>
+      </c>
+      <c r="K478" t="n">
+        <v>1</v>
+      </c>
+      <c r="L478" t="n">
+        <v>4</v>
+      </c>
+      <c r="M478" t="n">
+        <v>2</v>
+      </c>
+      <c r="N478" t="n">
+        <v>1</v>
+      </c>
+      <c r="O478" t="n">
+        <v>1</v>
+      </c>
+      <c r="P478" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>14</v>
+      </c>
+      <c r="R478" t="n">
+        <v>3</v>
+      </c>
+      <c r="S478" t="n">
+        <v>2</v>
+      </c>
+      <c r="T478" t="n">
+        <v>0</v>
+      </c>
+      <c r="U478" t="n">
+        <v>0</v>
+      </c>
+      <c r="V478" t="n">
+        <v>0</v>
+      </c>
+      <c r="W478" t="n">
+        <v>0</v>
+      </c>
+      <c r="X478" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:44.853814</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers - Union La Calera</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>90</v>
+      </c>
+      <c r="E479" t="n">
+        <v>4</v>
+      </c>
+      <c r="F479" t="n">
+        <v>7</v>
+      </c>
+      <c r="G479" t="n">
+        <v>26</v>
+      </c>
+      <c r="H479" t="n">
+        <v>12</v>
+      </c>
+      <c r="I479" t="n">
+        <v>4</v>
+      </c>
+      <c r="J479" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" t="n">
+        <v>5</v>
+      </c>
+      <c r="L479" t="n">
+        <v>14</v>
+      </c>
+      <c r="M479" t="n">
+        <v>7</v>
+      </c>
+      <c r="N479" t="n">
+        <v>3</v>
+      </c>
+      <c r="O479" t="n">
+        <v>4</v>
+      </c>
+      <c r="P479" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>12</v>
+      </c>
+      <c r="R479" t="n">
+        <v>5</v>
+      </c>
+      <c r="S479" t="n">
+        <v>1</v>
+      </c>
+      <c r="T479" t="n">
+        <v>0</v>
+      </c>
+      <c r="U479" t="n">
+        <v>0</v>
+      </c>
+      <c r="V479" t="n">
+        <v>0</v>
+      </c>
+      <c r="W479" t="n">
+        <v>0</v>
+      </c>
+      <c r="X479" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:10:52.959096</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Portuguesa RJ - Madureira</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>90</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1</v>
+      </c>
+      <c r="F480" t="n">
+        <v>10</v>
+      </c>
+      <c r="G480" t="n">
+        <v>20</v>
+      </c>
+      <c r="H480" t="n">
+        <v>10</v>
+      </c>
+      <c r="I480" t="n">
+        <v>8</v>
+      </c>
+      <c r="J480" t="n">
+        <v>0</v>
+      </c>
+      <c r="K480" t="n">
+        <v>9</v>
+      </c>
+      <c r="L480" t="n">
+        <v>13</v>
+      </c>
+      <c r="M480" t="n">
+        <v>6</v>
+      </c>
+      <c r="N480" t="n">
+        <v>3</v>
+      </c>
+      <c r="O480" t="n">
+        <v>1</v>
+      </c>
+      <c r="P480" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>7</v>
+      </c>
+      <c r="R480" t="n">
+        <v>4</v>
+      </c>
+      <c r="S480" t="n">
+        <v>5</v>
+      </c>
+      <c r="T480" t="n">
+        <v>0</v>
+      </c>
+      <c r="U480" t="n">
+        <v>0</v>
+      </c>
+      <c r="V480" t="n">
+        <v>0</v>
+      </c>
+      <c r="W480" t="n">
+        <v>0</v>
+      </c>
+      <c r="X480" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:00.953774</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Gremio - Mirassol</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>90</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1</v>
+      </c>
+      <c r="F481" t="n">
+        <v>6</v>
+      </c>
+      <c r="G481" t="n">
+        <v>24</v>
+      </c>
+      <c r="H481" t="n">
+        <v>4</v>
+      </c>
+      <c r="I481" t="n">
+        <v>6</v>
+      </c>
+      <c r="J481" t="n">
+        <v>1</v>
+      </c>
+      <c r="K481" t="n">
+        <v>1</v>
+      </c>
+      <c r="L481" t="n">
+        <v>11</v>
+      </c>
+      <c r="M481" t="n">
+        <v>3</v>
+      </c>
+      <c r="N481" t="n">
+        <v>3</v>
+      </c>
+      <c r="O481" t="n">
+        <v>0</v>
+      </c>
+      <c r="P481" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>13</v>
+      </c>
+      <c r="R481" t="n">
+        <v>1</v>
+      </c>
+      <c r="S481" t="n">
+        <v>3</v>
+      </c>
+      <c r="T481" t="n">
+        <v>0</v>
+      </c>
+      <c r="U481" t="n">
+        <v>0</v>
+      </c>
+      <c r="V481" t="n">
+        <v>0</v>
+      </c>
+      <c r="W481" t="n">
+        <v>0</v>
+      </c>
+      <c r="X481" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:09.035865</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Linhares - CTE Colatina</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>90</v>
+      </c>
+      <c r="E482" t="n">
+        <v>2</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0</v>
+      </c>
+      <c r="G482" t="n">
+        <v>0</v>
+      </c>
+      <c r="H482" t="n">
+        <v>0</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" t="n">
+        <v>2</v>
+      </c>
+      <c r="K482" t="n">
+        <v>0</v>
+      </c>
+      <c r="L482" t="n">
+        <v>0</v>
+      </c>
+      <c r="M482" t="n">
+        <v>0</v>
+      </c>
+      <c r="N482" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" t="n">
+        <v>0</v>
+      </c>
+      <c r="P482" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>0</v>
+      </c>
+      <c r="R482" t="n">
+        <v>0</v>
+      </c>
+      <c r="S482" t="n">
+        <v>0</v>
+      </c>
+      <c r="T482" t="n">
+        <v>0</v>
+      </c>
+      <c r="U482" t="n">
+        <v>0</v>
+      </c>
+      <c r="V482" t="n">
+        <v>0</v>
+      </c>
+      <c r="W482" t="n">
+        <v>0</v>
+      </c>
+      <c r="X482" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:17.035136</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Canada U20 - Jamaica U20</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>120</v>
+      </c>
+      <c r="E483" t="n">
+        <v>4</v>
+      </c>
+      <c r="F483" t="n">
+        <v>14</v>
+      </c>
+      <c r="G483" t="n">
+        <v>38</v>
+      </c>
+      <c r="H483" t="n">
+        <v>13</v>
+      </c>
+      <c r="I483" t="n">
+        <v>5</v>
+      </c>
+      <c r="J483" t="n">
+        <v>3</v>
+      </c>
+      <c r="K483" t="n">
+        <v>13</v>
+      </c>
+      <c r="L483" t="n">
+        <v>26</v>
+      </c>
+      <c r="M483" t="n">
+        <v>11</v>
+      </c>
+      <c r="N483" t="n">
+        <v>1</v>
+      </c>
+      <c r="O483" t="n">
+        <v>1</v>
+      </c>
+      <c r="P483" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>12</v>
+      </c>
+      <c r="R483" t="n">
+        <v>2</v>
+      </c>
+      <c r="S483" t="n">
+        <v>4</v>
+      </c>
+      <c r="T483" t="n">
+        <v>0</v>
+      </c>
+      <c r="U483" t="n">
+        <v>0</v>
+      </c>
+      <c r="V483" t="n">
+        <v>0</v>
+      </c>
+      <c r="W483" t="n">
+        <v>0</v>
+      </c>
+      <c r="X483" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:25.112328</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira - Metropolitanos FC</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>90</v>
+      </c>
+      <c r="E484" t="n">
+        <v>3</v>
+      </c>
+      <c r="F484" t="n">
+        <v>4</v>
+      </c>
+      <c r="G484" t="n">
+        <v>32</v>
+      </c>
+      <c r="H484" t="n">
+        <v>13</v>
+      </c>
+      <c r="I484" t="n">
+        <v>4</v>
+      </c>
+      <c r="J484" t="n">
+        <v>1</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" t="n">
+        <v>18</v>
+      </c>
+      <c r="M484" t="n">
+        <v>5</v>
+      </c>
+      <c r="N484" t="n">
+        <v>3</v>
+      </c>
+      <c r="O484" t="n">
+        <v>2</v>
+      </c>
+      <c r="P484" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>14</v>
+      </c>
+      <c r="R484" t="n">
+        <v>8</v>
+      </c>
+      <c r="S484" t="n">
+        <v>1</v>
+      </c>
+      <c r="T484" t="n">
+        <v>0</v>
+      </c>
+      <c r="U484" t="n">
+        <v>0</v>
+      </c>
+      <c r="V484" t="n">
+        <v>0</v>
+      </c>
+      <c r="W484" t="n">
+        <v>0</v>
+      </c>
+      <c r="X484" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:33.293768</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Richmond Kickers - NY Cosmos</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>90</v>
+      </c>
+      <c r="E485" t="n">
+        <v>2</v>
+      </c>
+      <c r="F485" t="n">
+        <v>8</v>
+      </c>
+      <c r="G485" t="n">
+        <v>24</v>
+      </c>
+      <c r="H485" t="n">
+        <v>9</v>
+      </c>
+      <c r="I485" t="n">
+        <v>5</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2</v>
+      </c>
+      <c r="K485" t="n">
+        <v>4</v>
+      </c>
+      <c r="L485" t="n">
+        <v>15</v>
+      </c>
+      <c r="M485" t="n">
+        <v>5</v>
+      </c>
+      <c r="N485" t="n">
+        <v>2</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>9</v>
+      </c>
+      <c r="R485" t="n">
+        <v>4</v>
+      </c>
+      <c r="S485" t="n">
+        <v>3</v>
+      </c>
+      <c r="T485" t="n">
+        <v>0</v>
+      </c>
+      <c r="U485" t="n">
+        <v>0</v>
+      </c>
+      <c r="V485" t="n">
+        <v>0</v>
+      </c>
+      <c r="W485" t="n">
+        <v>0</v>
+      </c>
+      <c r="X485" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:41.169672</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Penarol - Wanderers</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>90</v>
+      </c>
+      <c r="E486" t="n">
+        <v>6</v>
+      </c>
+      <c r="F486" t="n">
+        <v>8</v>
+      </c>
+      <c r="G486" t="n">
+        <v>20</v>
+      </c>
+      <c r="H486" t="n">
+        <v>11</v>
+      </c>
+      <c r="I486" t="n">
+        <v>2</v>
+      </c>
+      <c r="J486" t="n">
+        <v>5</v>
+      </c>
+      <c r="K486" t="n">
+        <v>4</v>
+      </c>
+      <c r="L486" t="n">
+        <v>11</v>
+      </c>
+      <c r="M486" t="n">
+        <v>7</v>
+      </c>
+      <c r="N486" t="n">
+        <v>1</v>
+      </c>
+      <c r="O486" t="n">
+        <v>1</v>
+      </c>
+      <c r="P486" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>9</v>
+      </c>
+      <c r="R486" t="n">
+        <v>4</v>
+      </c>
+      <c r="S486" t="n">
+        <v>1</v>
+      </c>
+      <c r="T486" t="n">
+        <v>0</v>
+      </c>
+      <c r="U486" t="n">
+        <v>0</v>
+      </c>
+      <c r="V486" t="n">
+        <v>0</v>
+      </c>
+      <c r="W486" t="n">
+        <v>0</v>
+      </c>
+      <c r="X486" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:49.201830</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Internacional de Bogota - Jaguares</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>90</v>
+      </c>
+      <c r="E487" t="n">
+        <v>1</v>
+      </c>
+      <c r="F487" t="n">
+        <v>9</v>
+      </c>
+      <c r="G487" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I487" t="n">
+        <v>2</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1</v>
+      </c>
+      <c r="K487" t="n">
+        <v>8</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" t="n">
+        <v>0</v>
+      </c>
+      <c r="N487" t="n">
+        <v>1</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>0</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0</v>
+      </c>
+      <c r="S487" t="n">
+        <v>1</v>
+      </c>
+      <c r="T487" t="n">
+        <v>0</v>
+      </c>
+      <c r="U487" t="n">
+        <v>0</v>
+      </c>
+      <c r="V487" t="n">
+        <v>0</v>
+      </c>
+      <c r="W487" t="n">
+        <v>0</v>
+      </c>
+      <c r="X487" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:11:57.220960</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Naples - Alta</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>90</v>
+      </c>
+      <c r="E488" t="n">
+        <v>3</v>
+      </c>
+      <c r="F488" t="n">
+        <v>15</v>
+      </c>
+      <c r="G488" t="n">
+        <v>21</v>
+      </c>
+      <c r="H488" t="n">
+        <v>8</v>
+      </c>
+      <c r="I488" t="n">
+        <v>8</v>
+      </c>
+      <c r="J488" t="n">
+        <v>2</v>
+      </c>
+      <c r="K488" t="n">
+        <v>5</v>
+      </c>
+      <c r="L488" t="n">
+        <v>10</v>
+      </c>
+      <c r="M488" t="n">
+        <v>3</v>
+      </c>
+      <c r="N488" t="n">
+        <v>4</v>
+      </c>
+      <c r="O488" t="n">
+        <v>1</v>
+      </c>
+      <c r="P488" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>11</v>
+      </c>
+      <c r="R488" t="n">
+        <v>5</v>
+      </c>
+      <c r="S488" t="n">
+        <v>4</v>
+      </c>
+      <c r="T488" t="n">
+        <v>0</v>
+      </c>
+      <c r="U488" t="n">
+        <v>0</v>
+      </c>
+      <c r="V488" t="n">
+        <v>0</v>
+      </c>
+      <c r="W488" t="n">
+        <v>0</v>
+      </c>
+      <c r="X488" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:07.629063</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Inter Miami - Atletico San Luis</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>90</v>
+      </c>
+      <c r="E489" t="n">
+        <v>6</v>
+      </c>
+      <c r="F489" t="n">
+        <v>7</v>
+      </c>
+      <c r="G489" t="n">
+        <v>25</v>
+      </c>
+      <c r="H489" t="n">
+        <v>12</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1</v>
+      </c>
+      <c r="J489" t="n">
+        <v>4</v>
+      </c>
+      <c r="K489" t="n">
+        <v>1</v>
+      </c>
+      <c r="L489" t="n">
+        <v>8</v>
+      </c>
+      <c r="M489" t="n">
+        <v>5</v>
+      </c>
+      <c r="N489" t="n">
+        <v>1</v>
+      </c>
+      <c r="O489" t="n">
+        <v>2</v>
+      </c>
+      <c r="P489" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>17</v>
+      </c>
+      <c r="R489" t="n">
+        <v>7</v>
+      </c>
+      <c r="S489" t="n">
+        <v>0</v>
+      </c>
+      <c r="T489" t="n">
+        <v>0</v>
+      </c>
+      <c r="U489" t="n">
+        <v>0</v>
+      </c>
+      <c r="V489" t="n">
+        <v>0</v>
+      </c>
+      <c r="W489" t="n">
+        <v>0</v>
+      </c>
+      <c r="X489" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:15.575738</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Monterrey - Orlando City SC</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>90</v>
+      </c>
+      <c r="E490" t="n">
+        <v>3</v>
+      </c>
+      <c r="F490" t="n">
+        <v>7</v>
+      </c>
+      <c r="G490" t="n">
+        <v>22</v>
+      </c>
+      <c r="H490" t="n">
+        <v>5</v>
+      </c>
+      <c r="I490" t="n">
+        <v>8</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>2</v>
+      </c>
+      <c r="L490" t="n">
+        <v>11</v>
+      </c>
+      <c r="M490" t="n">
+        <v>2</v>
+      </c>
+      <c r="N490" t="n">
+        <v>5</v>
+      </c>
+      <c r="O490" t="n">
+        <v>2</v>
+      </c>
+      <c r="P490" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>11</v>
+      </c>
+      <c r="R490" t="n">
+        <v>3</v>
+      </c>
+      <c r="S490" t="n">
+        <v>3</v>
+      </c>
+      <c r="T490" t="n">
+        <v>0</v>
+      </c>
+      <c r="U490" t="n">
+        <v>0</v>
+      </c>
+      <c r="V490" t="n">
+        <v>0</v>
+      </c>
+      <c r="W490" t="n">
+        <v>0</v>
+      </c>
+      <c r="X490" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:23.668855</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Bolívar - Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>90</v>
+      </c>
+      <c r="E491" t="n">
+        <v>3</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0</v>
+      </c>
+      <c r="G491" t="n">
+        <v>0</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2</v>
+      </c>
+      <c r="K491" t="n">
+        <v>0</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" t="n">
+        <v>0</v>
+      </c>
+      <c r="N491" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" t="n">
+        <v>1</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>0</v>
+      </c>
+      <c r="R491" t="n">
+        <v>0</v>
+      </c>
+      <c r="S491" t="n">
+        <v>0</v>
+      </c>
+      <c r="T491" t="n">
+        <v>0</v>
+      </c>
+      <c r="U491" t="n">
+        <v>0</v>
+      </c>
+      <c r="V491" t="n">
+        <v>0</v>
+      </c>
+      <c r="W491" t="n">
+        <v>0</v>
+      </c>
+      <c r="X491" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:31.635426</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Santa Fe - Union Magdalena</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>90</v>
+      </c>
+      <c r="E492" t="n">
+        <v>2</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" t="n">
+        <v>0</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0</v>
+      </c>
+      <c r="J492" t="n">
+        <v>2</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L492" t="n">
+        <v>0</v>
+      </c>
+      <c r="M492" t="n">
+        <v>0</v>
+      </c>
+      <c r="N492" t="n">
+        <v>0</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>0</v>
+      </c>
+      <c r="R492" t="n">
+        <v>0</v>
+      </c>
+      <c r="S492" t="n">
+        <v>0</v>
+      </c>
+      <c r="T492" t="n">
+        <v>0</v>
+      </c>
+      <c r="U492" t="n">
+        <v>0</v>
+      </c>
+      <c r="V492" t="n">
+        <v>0</v>
+      </c>
+      <c r="W492" t="n">
+        <v>0</v>
+      </c>
+      <c r="X492" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:39.742757</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>LDU Portoviejo - Barcelona SC</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>90</v>
+      </c>
+      <c r="E493" t="n">
+        <v>1</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0</v>
+      </c>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>0</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>0</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" t="n">
+        <v>0</v>
+      </c>
+      <c r="O493" t="n">
+        <v>1</v>
+      </c>
+      <c r="P493" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>0</v>
+      </c>
+      <c r="R493" t="n">
+        <v>0</v>
+      </c>
+      <c r="S493" t="n">
+        <v>0</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="n">
+        <v>0</v>
+      </c>
+      <c r="V493" t="n">
+        <v>0</v>
+      </c>
+      <c r="W493" t="n">
+        <v>0</v>
+      </c>
+      <c r="X493" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:47.787190</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>UMECIT - CD Olimpia</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>90</v>
+      </c>
+      <c r="E494" t="n">
+        <v>3</v>
+      </c>
+      <c r="F494" t="n">
+        <v>0</v>
+      </c>
+      <c r="G494" t="n">
+        <v>0</v>
+      </c>
+      <c r="H494" t="n">
+        <v>0</v>
+      </c>
+      <c r="I494" t="n">
+        <v>0</v>
+      </c>
+      <c r="J494" t="n">
+        <v>1</v>
+      </c>
+      <c r="K494" t="n">
+        <v>0</v>
+      </c>
+      <c r="L494" t="n">
+        <v>0</v>
+      </c>
+      <c r="M494" t="n">
+        <v>0</v>
+      </c>
+      <c r="N494" t="n">
+        <v>0</v>
+      </c>
+      <c r="O494" t="n">
+        <v>2</v>
+      </c>
+      <c r="P494" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>0</v>
+      </c>
+      <c r="R494" t="n">
+        <v>0</v>
+      </c>
+      <c r="S494" t="n">
+        <v>0</v>
+      </c>
+      <c r="T494" t="n">
+        <v>0</v>
+      </c>
+      <c r="U494" t="n">
+        <v>0</v>
+      </c>
+      <c r="V494" t="n">
+        <v>0</v>
+      </c>
+      <c r="W494" t="n">
+        <v>0</v>
+      </c>
+      <c r="X494" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:12:55.843705</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Cibao - Cavalier</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>90</v>
+      </c>
+      <c r="E495" t="n">
+        <v>0</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0</v>
+      </c>
+      <c r="G495" t="n">
+        <v>0</v>
+      </c>
+      <c r="H495" t="n">
+        <v>0</v>
+      </c>
+      <c r="I495" t="n">
+        <v>0</v>
+      </c>
+      <c r="J495" t="n">
+        <v>0</v>
+      </c>
+      <c r="K495" t="n">
+        <v>0</v>
+      </c>
+      <c r="L495" t="n">
+        <v>0</v>
+      </c>
+      <c r="M495" t="n">
+        <v>0</v>
+      </c>
+      <c r="N495" t="n">
+        <v>0</v>
+      </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
+      <c r="P495" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>0</v>
+      </c>
+      <c r="R495" t="n">
+        <v>0</v>
+      </c>
+      <c r="S495" t="n">
+        <v>0</v>
+      </c>
+      <c r="T495" t="n">
+        <v>0</v>
+      </c>
+      <c r="U495" t="n">
+        <v>0</v>
+      </c>
+      <c r="V495" t="n">
+        <v>0</v>
+      </c>
+      <c r="W495" t="n">
+        <v>0</v>
+      </c>
+      <c r="X495" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:03.814861</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Colombia U21 - Venezuela U21</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>90</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1</v>
+      </c>
+      <c r="F496" t="n">
+        <v>0</v>
+      </c>
+      <c r="G496" t="n">
+        <v>0</v>
+      </c>
+      <c r="H496" t="n">
+        <v>0</v>
+      </c>
+      <c r="I496" t="n">
+        <v>1</v>
+      </c>
+      <c r="J496" t="n">
+        <v>0</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0</v>
+      </c>
+      <c r="L496" t="n">
+        <v>0</v>
+      </c>
+      <c r="M496" t="n">
+        <v>0</v>
+      </c>
+      <c r="N496" t="n">
+        <v>1</v>
+      </c>
+      <c r="O496" t="n">
+        <v>1</v>
+      </c>
+      <c r="P496" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>0</v>
+      </c>
+      <c r="R496" t="n">
+        <v>0</v>
+      </c>
+      <c r="S496" t="n">
+        <v>0</v>
+      </c>
+      <c r="T496" t="n">
+        <v>0</v>
+      </c>
+      <c r="U496" t="n">
+        <v>0</v>
+      </c>
+      <c r="V496" t="n">
+        <v>0</v>
+      </c>
+      <c r="W496" t="n">
+        <v>0</v>
+      </c>
+      <c r="X496" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:11.845347</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Tigre - Belgrano Cordoba</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>90</v>
+      </c>
+      <c r="E497" t="n">
+        <v>0</v>
+      </c>
+      <c r="F497" t="n">
+        <v>8</v>
+      </c>
+      <c r="G497" t="n">
+        <v>33</v>
+      </c>
+      <c r="H497" t="n">
+        <v>11</v>
+      </c>
+      <c r="I497" t="n">
+        <v>5</v>
+      </c>
+      <c r="J497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" t="n">
+        <v>4</v>
+      </c>
+      <c r="L497" t="n">
+        <v>18</v>
+      </c>
+      <c r="M497" t="n">
+        <v>5</v>
+      </c>
+      <c r="N497" t="n">
+        <v>1</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>15</v>
+      </c>
+      <c r="R497" t="n">
+        <v>6</v>
+      </c>
+      <c r="S497" t="n">
+        <v>4</v>
+      </c>
+      <c r="T497" t="n">
+        <v>0</v>
+      </c>
+      <c r="U497" t="n">
+        <v>0</v>
+      </c>
+      <c r="V497" t="n">
+        <v>0</v>
+      </c>
+      <c r="W497" t="n">
+        <v>0</v>
+      </c>
+      <c r="X497" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:19.887420</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>FC Tulsa - Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>90</v>
+      </c>
+      <c r="E498" t="n">
+        <v>1</v>
+      </c>
+      <c r="F498" t="n">
+        <v>6</v>
+      </c>
+      <c r="G498" t="n">
+        <v>18</v>
+      </c>
+      <c r="H498" t="n">
+        <v>7</v>
+      </c>
+      <c r="I498" t="n">
+        <v>3</v>
+      </c>
+      <c r="J498" t="n">
+        <v>1</v>
+      </c>
+      <c r="K498" t="n">
+        <v>4</v>
+      </c>
+      <c r="L498" t="n">
+        <v>8</v>
+      </c>
+      <c r="M498" t="n">
+        <v>3</v>
+      </c>
+      <c r="N498" t="n">
+        <v>2</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
+      <c r="P498" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>10</v>
+      </c>
+      <c r="R498" t="n">
+        <v>4</v>
+      </c>
+      <c r="S498" t="n">
+        <v>1</v>
+      </c>
+      <c r="T498" t="n">
+        <v>0</v>
+      </c>
+      <c r="U498" t="n">
+        <v>0</v>
+      </c>
+      <c r="V498" t="n">
+        <v>0</v>
+      </c>
+      <c r="W498" t="n">
+        <v>0</v>
+      </c>
+      <c r="X498" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:29.742255</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>FC Dallas - Club Queretaro</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>90</v>
+      </c>
+      <c r="E499" t="n">
+        <v>2</v>
+      </c>
+      <c r="F499" t="n">
+        <v>13</v>
+      </c>
+      <c r="G499" t="n">
+        <v>30</v>
+      </c>
+      <c r="H499" t="n">
+        <v>16</v>
+      </c>
+      <c r="I499" t="n">
+        <v>6</v>
+      </c>
+      <c r="J499" t="n">
+        <v>2</v>
+      </c>
+      <c r="K499" t="n">
+        <v>6</v>
+      </c>
+      <c r="L499" t="n">
+        <v>12</v>
+      </c>
+      <c r="M499" t="n">
+        <v>8</v>
+      </c>
+      <c r="N499" t="n">
+        <v>3</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
+      <c r="P499" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>18</v>
+      </c>
+      <c r="R499" t="n">
+        <v>8</v>
+      </c>
+      <c r="S499" t="n">
+        <v>3</v>
+      </c>
+      <c r="T499" t="n">
+        <v>0</v>
+      </c>
+      <c r="U499" t="n">
+        <v>0</v>
+      </c>
+      <c r="V499" t="n">
+        <v>0</v>
+      </c>
+      <c r="W499" t="n">
+        <v>0</v>
+      </c>
+      <c r="X499" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:37.723293</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Nashville SC - Leon</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>90</v>
+      </c>
+      <c r="E500" t="n">
+        <v>1</v>
+      </c>
+      <c r="F500" t="n">
+        <v>9</v>
+      </c>
+      <c r="G500" t="n">
+        <v>13</v>
+      </c>
+      <c r="H500" t="n">
+        <v>4</v>
+      </c>
+      <c r="I500" t="n">
+        <v>5</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" t="n">
+        <v>4</v>
+      </c>
+      <c r="L500" t="n">
+        <v>6</v>
+      </c>
+      <c r="M500" t="n">
+        <v>2</v>
+      </c>
+      <c r="N500" t="n">
+        <v>3</v>
+      </c>
+      <c r="O500" t="n">
+        <v>1</v>
+      </c>
+      <c r="P500" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>7</v>
+      </c>
+      <c r="R500" t="n">
+        <v>2</v>
+      </c>
+      <c r="S500" t="n">
+        <v>2</v>
+      </c>
+      <c r="T500" t="n">
+        <v>0</v>
+      </c>
+      <c r="U500" t="n">
+        <v>0</v>
+      </c>
+      <c r="V500" t="n">
+        <v>0</v>
+      </c>
+      <c r="W500" t="n">
+        <v>0</v>
+      </c>
+      <c r="X500" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:45.696795</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Fluminense - Vasco DA Gama</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>90</v>
+      </c>
+      <c r="E501" t="n">
+        <v>4</v>
+      </c>
+      <c r="F501" t="n">
+        <v>6</v>
+      </c>
+      <c r="G501" t="n">
+        <v>27</v>
+      </c>
+      <c r="H501" t="n">
+        <v>11</v>
+      </c>
+      <c r="I501" t="n">
+        <v>8</v>
+      </c>
+      <c r="J501" t="n">
+        <v>1</v>
+      </c>
+      <c r="K501" t="n">
+        <v>1</v>
+      </c>
+      <c r="L501" t="n">
+        <v>13</v>
+      </c>
+      <c r="M501" t="n">
+        <v>4</v>
+      </c>
+      <c r="N501" t="n">
+        <v>3</v>
+      </c>
+      <c r="O501" t="n">
+        <v>3</v>
+      </c>
+      <c r="P501" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>14</v>
+      </c>
+      <c r="R501" t="n">
+        <v>7</v>
+      </c>
+      <c r="S501" t="n">
+        <v>5</v>
+      </c>
+      <c r="T501" t="n">
+        <v>0</v>
+      </c>
+      <c r="U501" t="n">
+        <v>0</v>
+      </c>
+      <c r="V501" t="n">
+        <v>0</v>
+      </c>
+      <c r="W501" t="n">
+        <v>0</v>
+      </c>
+      <c r="X501" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:13:53.795969</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Fortaleza EC - Palmeiras</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>90</v>
+      </c>
+      <c r="E502" t="n">
+        <v>5</v>
+      </c>
+      <c r="F502" t="n">
+        <v>10</v>
+      </c>
+      <c r="G502" t="n">
+        <v>26</v>
+      </c>
+      <c r="H502" t="n">
+        <v>8</v>
+      </c>
+      <c r="I502" t="n">
+        <v>1</v>
+      </c>
+      <c r="J502" t="n">
+        <v>3</v>
+      </c>
+      <c r="K502" t="n">
+        <v>6</v>
+      </c>
+      <c r="L502" t="n">
+        <v>12</v>
+      </c>
+      <c r="M502" t="n">
+        <v>4</v>
+      </c>
+      <c r="N502" t="n">
+        <v>1</v>
+      </c>
+      <c r="O502" t="n">
+        <v>2</v>
+      </c>
+      <c r="P502" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>14</v>
+      </c>
+      <c r="R502" t="n">
+        <v>4</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0</v>
+      </c>
+      <c r="U502" t="n">
+        <v>0</v>
+      </c>
+      <c r="V502" t="n">
+        <v>0</v>
+      </c>
+      <c r="W502" t="n">
+        <v>0</v>
+      </c>
+      <c r="X502" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:01.768822</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido - San Marcos de Arica</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>90</v>
+      </c>
+      <c r="E503" t="n">
+        <v>1</v>
+      </c>
+      <c r="F503" t="n">
+        <v>8</v>
+      </c>
+      <c r="G503" t="n">
+        <v>23</v>
+      </c>
+      <c r="H503" t="n">
+        <v>6</v>
+      </c>
+      <c r="I503" t="n">
+        <v>4</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="n">
+        <v>6</v>
+      </c>
+      <c r="L503" t="n">
+        <v>12</v>
+      </c>
+      <c r="M503" t="n">
+        <v>3</v>
+      </c>
+      <c r="N503" t="n">
+        <v>2</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>11</v>
+      </c>
+      <c r="R503" t="n">
+        <v>3</v>
+      </c>
+      <c r="S503" t="n">
+        <v>2</v>
+      </c>
+      <c r="T503" t="n">
+        <v>0</v>
+      </c>
+      <c r="U503" t="n">
+        <v>0</v>
+      </c>
+      <c r="V503" t="n">
+        <v>0</v>
+      </c>
+      <c r="W503" t="n">
+        <v>0</v>
+      </c>
+      <c r="X503" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:09.854374</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Deportes Iquique - Deportes Limache</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>90</v>
+      </c>
+      <c r="E504" t="n">
+        <v>4</v>
+      </c>
+      <c r="F504" t="n">
+        <v>9</v>
+      </c>
+      <c r="G504" t="n">
+        <v>25</v>
+      </c>
+      <c r="H504" t="n">
+        <v>12</v>
+      </c>
+      <c r="I504" t="n">
+        <v>5</v>
+      </c>
+      <c r="J504" t="n">
+        <v>3</v>
+      </c>
+      <c r="K504" t="n">
+        <v>3</v>
+      </c>
+      <c r="L504" t="n">
+        <v>12</v>
+      </c>
+      <c r="M504" t="n">
+        <v>8</v>
+      </c>
+      <c r="N504" t="n">
+        <v>2</v>
+      </c>
+      <c r="O504" t="n">
+        <v>1</v>
+      </c>
+      <c r="P504" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>13</v>
+      </c>
+      <c r="R504" t="n">
+        <v>4</v>
+      </c>
+      <c r="S504" t="n">
+        <v>3</v>
+      </c>
+      <c r="T504" t="n">
+        <v>0</v>
+      </c>
+      <c r="U504" t="n">
+        <v>0</v>
+      </c>
+      <c r="V504" t="n">
+        <v>0</v>
+      </c>
+      <c r="W504" t="n">
+        <v>0</v>
+      </c>
+      <c r="X504" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:17.901841</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive - Monterey Bay</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>90</v>
+      </c>
+      <c r="E505" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" t="n">
+        <v>9</v>
+      </c>
+      <c r="G505" t="n">
+        <v>23</v>
+      </c>
+      <c r="H505" t="n">
+        <v>6</v>
+      </c>
+      <c r="I505" t="n">
+        <v>4</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="n">
+        <v>6</v>
+      </c>
+      <c r="L505" t="n">
+        <v>17</v>
+      </c>
+      <c r="M505" t="n">
+        <v>5</v>
+      </c>
+      <c r="N505" t="n">
+        <v>2</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>6</v>
+      </c>
+      <c r="R505" t="n">
+        <v>1</v>
+      </c>
+      <c r="S505" t="n">
+        <v>2</v>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>0</v>
+      </c>
+      <c r="V505" t="n">
+        <v>0</v>
+      </c>
+      <c r="W505" t="n">
+        <v>0</v>
+      </c>
+      <c r="X505" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:25.920766</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Once Caldas - America de Cali</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>90</v>
+      </c>
+      <c r="E506" t="n">
+        <v>1</v>
+      </c>
+      <c r="F506" t="n">
+        <v>8</v>
+      </c>
+      <c r="G506" t="n">
+        <v>30</v>
+      </c>
+      <c r="H506" t="n">
+        <v>10</v>
+      </c>
+      <c r="I506" t="n">
+        <v>6</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" t="n">
+        <v>3</v>
+      </c>
+      <c r="L506" t="n">
+        <v>13</v>
+      </c>
+      <c r="M506" t="n">
+        <v>5</v>
+      </c>
+      <c r="N506" t="n">
+        <v>2</v>
+      </c>
+      <c r="O506" t="n">
+        <v>1</v>
+      </c>
+      <c r="P506" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>17</v>
+      </c>
+      <c r="R506" t="n">
+        <v>5</v>
+      </c>
+      <c r="S506" t="n">
+        <v>4</v>
+      </c>
+      <c r="T506" t="n">
+        <v>0</v>
+      </c>
+      <c r="U506" t="n">
+        <v>0</v>
+      </c>
+      <c r="V506" t="n">
+        <v>0</v>
+      </c>
+      <c r="W506" t="n">
+        <v>0</v>
+      </c>
+      <c r="X506" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:34.021823</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Denver Summit W - North Carolina Courage W</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>90</v>
+      </c>
+      <c r="E507" t="n">
+        <v>2</v>
+      </c>
+      <c r="F507" t="n">
+        <v>10</v>
+      </c>
+      <c r="G507" t="n">
+        <v>31</v>
+      </c>
+      <c r="H507" t="n">
+        <v>15</v>
+      </c>
+      <c r="I507" t="n">
+        <v>2</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" t="n">
+        <v>6</v>
+      </c>
+      <c r="L507" t="n">
+        <v>17</v>
+      </c>
+      <c r="M507" t="n">
+        <v>6</v>
+      </c>
+      <c r="N507" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" t="n">
+        <v>2</v>
+      </c>
+      <c r="P507" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>14</v>
+      </c>
+      <c r="R507" t="n">
+        <v>9</v>
+      </c>
+      <c r="S507" t="n">
+        <v>2</v>
+      </c>
+      <c r="T507" t="n">
+        <v>0</v>
+      </c>
+      <c r="U507" t="n">
+        <v>0</v>
+      </c>
+      <c r="V507" t="n">
+        <v>0</v>
+      </c>
+      <c r="W507" t="n">
+        <v>0</v>
+      </c>
+      <c r="X507" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:42.035094</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Toluca - Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>90</v>
+      </c>
+      <c r="E508" t="n">
+        <v>3</v>
+      </c>
+      <c r="F508" t="n">
+        <v>13</v>
+      </c>
+      <c r="G508" t="n">
+        <v>42</v>
+      </c>
+      <c r="H508" t="n">
+        <v>19</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="n">
+        <v>3</v>
+      </c>
+      <c r="K508" t="n">
+        <v>12</v>
+      </c>
+      <c r="L508" t="n">
+        <v>38</v>
+      </c>
+      <c r="M508" t="n">
+        <v>17</v>
+      </c>
+      <c r="N508" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>4</v>
+      </c>
+      <c r="R508" t="n">
+        <v>2</v>
+      </c>
+      <c r="S508" t="n">
+        <v>0</v>
+      </c>
+      <c r="T508" t="n">
+        <v>0</v>
+      </c>
+      <c r="U508" t="n">
+        <v>0</v>
+      </c>
+      <c r="V508" t="n">
+        <v>0</v>
+      </c>
+      <c r="W508" t="n">
+        <v>0</v>
+      </c>
+      <c r="X508" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:50.105999</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Alianza - CS Herediano</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>90</v>
+      </c>
+      <c r="E509" t="n">
+        <v>1</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" t="n">
+        <v>0</v>
+      </c>
+      <c r="H509" t="n">
+        <v>0</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" t="n">
+        <v>1</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" t="n">
+        <v>0</v>
+      </c>
+      <c r="M509" t="n">
+        <v>0</v>
+      </c>
+      <c r="N509" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>0</v>
+      </c>
+      <c r="R509" t="n">
+        <v>0</v>
+      </c>
+      <c r="S509" t="n">
+        <v>0</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="n">
+        <v>0</v>
+      </c>
+      <c r="V509" t="n">
+        <v>0</v>
+      </c>
+      <c r="W509" t="n">
+        <v>0</v>
+      </c>
+      <c r="X509" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:14:58.087963</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Deportivo Saprissa - Alianza FC</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>90</v>
+      </c>
+      <c r="E510" t="n">
+        <v>3</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H510" t="n">
+        <v>0</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" t="n">
+        <v>2</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="n">
+        <v>0</v>
+      </c>
+      <c r="M510" t="n">
+        <v>0</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>1</v>
+      </c>
+      <c r="P510" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>0</v>
+      </c>
+      <c r="R510" t="n">
+        <v>0</v>
+      </c>
+      <c r="S510" t="n">
+        <v>0</v>
+      </c>
+      <c r="T510" t="n">
+        <v>0</v>
+      </c>
+      <c r="U510" t="n">
+        <v>0</v>
+      </c>
+      <c r="V510" t="n">
+        <v>0</v>
+      </c>
+      <c r="W510" t="n">
+        <v>0</v>
+      </c>
+      <c r="X510" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:06.187263</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Mexico U20 - Panama U20</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>90</v>
+      </c>
+      <c r="E511" t="n">
+        <v>4</v>
+      </c>
+      <c r="F511" t="n">
+        <v>8</v>
+      </c>
+      <c r="G511" t="n">
+        <v>23</v>
+      </c>
+      <c r="H511" t="n">
+        <v>6</v>
+      </c>
+      <c r="I511" t="n">
+        <v>2</v>
+      </c>
+      <c r="J511" t="n">
+        <v>4</v>
+      </c>
+      <c r="K511" t="n">
+        <v>6</v>
+      </c>
+      <c r="L511" t="n">
+        <v>15</v>
+      </c>
+      <c r="M511" t="n">
+        <v>5</v>
+      </c>
+      <c r="N511" t="n">
+        <v>0</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>8</v>
+      </c>
+      <c r="R511" t="n">
+        <v>1</v>
+      </c>
+      <c r="S511" t="n">
+        <v>2</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="n">
+        <v>0</v>
+      </c>
+      <c r="V511" t="n">
+        <v>0</v>
+      </c>
+      <c r="W511" t="n">
+        <v>0</v>
+      </c>
+      <c r="X511" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:14.158738</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights - Oakland Roots</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>90</v>
+      </c>
+      <c r="E512" t="n">
+        <v>0</v>
+      </c>
+      <c r="F512" t="n">
+        <v>13</v>
+      </c>
+      <c r="G512" t="n">
+        <v>23</v>
+      </c>
+      <c r="H512" t="n">
+        <v>7</v>
+      </c>
+      <c r="I512" t="n">
+        <v>5</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" t="n">
+        <v>5</v>
+      </c>
+      <c r="L512" t="n">
+        <v>14</v>
+      </c>
+      <c r="M512" t="n">
+        <v>5</v>
+      </c>
+      <c r="N512" t="n">
+        <v>1</v>
+      </c>
+      <c r="O512" t="n">
+        <v>0</v>
+      </c>
+      <c r="P512" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>9</v>
+      </c>
+      <c r="R512" t="n">
+        <v>2</v>
+      </c>
+      <c r="S512" t="n">
+        <v>4</v>
+      </c>
+      <c r="T512" t="n">
+        <v>0</v>
+      </c>
+      <c r="U512" t="n">
+        <v>0</v>
+      </c>
+      <c r="V512" t="n">
+        <v>0</v>
+      </c>
+      <c r="W512" t="n">
+        <v>0</v>
+      </c>
+      <c r="X512" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:22.222496</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Los Angeles FC - Guadalajara Chivas</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>120</v>
+      </c>
+      <c r="E513" t="n">
+        <v>2</v>
+      </c>
+      <c r="F513" t="n">
+        <v>7</v>
+      </c>
+      <c r="G513" t="n">
+        <v>28</v>
+      </c>
+      <c r="H513" t="n">
+        <v>13</v>
+      </c>
+      <c r="I513" t="n">
+        <v>3</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="n">
+        <v>2</v>
+      </c>
+      <c r="L513" t="n">
+        <v>9</v>
+      </c>
+      <c r="M513" t="n">
+        <v>5</v>
+      </c>
+      <c r="N513" t="n">
+        <v>1</v>
+      </c>
+      <c r="O513" t="n">
+        <v>1</v>
+      </c>
+      <c r="P513" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>19</v>
+      </c>
+      <c r="R513" t="n">
+        <v>8</v>
+      </c>
+      <c r="S513" t="n">
+        <v>2</v>
+      </c>
+      <c r="T513" t="n">
+        <v>0</v>
+      </c>
+      <c r="U513" t="n">
+        <v>0</v>
+      </c>
+      <c r="V513" t="n">
+        <v>0</v>
+      </c>
+      <c r="W513" t="n">
+        <v>0</v>
+      </c>
+      <c r="X513" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:30.314634</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Persija - Arema FC</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>90</v>
+      </c>
+      <c r="E514" t="n">
+        <v>4</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>6</v>
+      </c>
+      <c r="J514" t="n">
+        <v>3</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" t="n">
+        <v>1</v>
+      </c>
+      <c r="O514" t="n">
+        <v>1</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>0</v>
+      </c>
+      <c r="R514" t="n">
+        <v>0</v>
+      </c>
+      <c r="S514" t="n">
+        <v>5</v>
+      </c>
+      <c r="T514" t="n">
+        <v>0</v>
+      </c>
+      <c r="U514" t="n">
+        <v>0</v>
+      </c>
+      <c r="V514" t="n">
+        <v>0</v>
+      </c>
+      <c r="W514" t="n">
+        <v>0</v>
+      </c>
+      <c r="X514" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:38.604982</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Salisbury United - South Adelaide Panthers</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>90</v>
+      </c>
+      <c r="E515" t="n">
+        <v>5</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0</v>
+      </c>
+      <c r="G515" t="n">
+        <v>0</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0</v>
+      </c>
+      <c r="J515" t="n">
+        <v>2</v>
+      </c>
+      <c r="K515" t="n">
+        <v>0</v>
+      </c>
+      <c r="L515" t="n">
+        <v>0</v>
+      </c>
+      <c r="M515" t="n">
+        <v>0</v>
+      </c>
+      <c r="N515" t="n">
+        <v>0</v>
+      </c>
+      <c r="O515" t="n">
+        <v>3</v>
+      </c>
+      <c r="P515" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>0</v>
+      </c>
+      <c r="R515" t="n">
+        <v>0</v>
+      </c>
+      <c r="S515" t="n">
+        <v>0</v>
+      </c>
+      <c r="T515" t="n">
+        <v>0</v>
+      </c>
+      <c r="U515" t="n">
+        <v>0</v>
+      </c>
+      <c r="V515" t="n">
+        <v>0</v>
+      </c>
+      <c r="W515" t="n">
+        <v>0</v>
+      </c>
+      <c r="X515" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:46.443640</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Akademiya Ontustik - Khan Tengri</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>90</v>
+      </c>
+      <c r="E516" t="n">
+        <v>4</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" t="n">
+        <v>0</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" t="n">
+        <v>3</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" t="n">
+        <v>0</v>
+      </c>
+      <c r="M516" t="n">
+        <v>0</v>
+      </c>
+      <c r="N516" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" t="n">
+        <v>1</v>
+      </c>
+      <c r="P516" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>0</v>
+      </c>
+      <c r="R516" t="n">
+        <v>0</v>
+      </c>
+      <c r="S516" t="n">
+        <v>0</v>
+      </c>
+      <c r="T516" t="n">
+        <v>0</v>
+      </c>
+      <c r="U516" t="n">
+        <v>0</v>
+      </c>
+      <c r="V516" t="n">
+        <v>0</v>
+      </c>
+      <c r="W516" t="n">
+        <v>0</v>
+      </c>
+      <c r="X516" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:15:54.420378</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Yelimay Semey 2 - Sport Academy Kairat</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>90</v>
+      </c>
+      <c r="E517" t="n">
+        <v>1</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" t="n">
+        <v>1</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>0</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0</v>
+      </c>
+      <c r="S517" t="n">
+        <v>0</v>
+      </c>
+      <c r="T517" t="n">
+        <v>0</v>
+      </c>
+      <c r="U517" t="n">
+        <v>0</v>
+      </c>
+      <c r="V517" t="n">
+        <v>0</v>
+      </c>
+      <c r="W517" t="n">
+        <v>0</v>
+      </c>
+      <c r="X517" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:02.517103</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Sandefjord U19 - Åsane U19</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>0</v>
+      </c>
+      <c r="E518" t="n">
+        <v>0</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0</v>
+      </c>
+      <c r="M518" t="n">
+        <v>0</v>
+      </c>
+      <c r="N518" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>0</v>
+      </c>
+      <c r="R518" t="n">
+        <v>0</v>
+      </c>
+      <c r="S518" t="n">
+        <v>0</v>
+      </c>
+      <c r="T518" t="n">
+        <v>0</v>
+      </c>
+      <c r="U518" t="n">
+        <v>0</v>
+      </c>
+      <c r="V518" t="n">
+        <v>0</v>
+      </c>
+      <c r="W518" t="n">
+        <v>0</v>
+      </c>
+      <c r="X518" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:10.547332</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Lillestrøm U19 - Aalesunds U19</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>6-0</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>90</v>
+      </c>
+      <c r="E519" t="n">
+        <v>6</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0</v>
+      </c>
+      <c r="G519" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" t="n">
+        <v>0</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" t="n">
+        <v>6</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" t="n">
+        <v>0</v>
+      </c>
+      <c r="M519" t="n">
+        <v>0</v>
+      </c>
+      <c r="N519" t="n">
+        <v>0</v>
+      </c>
+      <c r="O519" t="n">
+        <v>0</v>
+      </c>
+      <c r="P519" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>0</v>
+      </c>
+      <c r="R519" t="n">
+        <v>0</v>
+      </c>
+      <c r="S519" t="n">
+        <v>0</v>
+      </c>
+      <c r="T519" t="n">
+        <v>0</v>
+      </c>
+      <c r="U519" t="n">
+        <v>0</v>
+      </c>
+      <c r="V519" t="n">
+        <v>0</v>
+      </c>
+      <c r="W519" t="n">
+        <v>0</v>
+      </c>
+      <c r="X519" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:18.870591</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Betlemi - Irao</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>90</v>
+      </c>
+      <c r="E520" t="n">
+        <v>2</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" t="n">
+        <v>0</v>
+      </c>
+      <c r="H520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" t="n">
+        <v>1</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" t="n">
+        <v>0</v>
+      </c>
+      <c r="N520" t="n">
+        <v>0</v>
+      </c>
+      <c r="O520" t="n">
+        <v>1</v>
+      </c>
+      <c r="P520" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>0</v>
+      </c>
+      <c r="R520" t="n">
+        <v>0</v>
+      </c>
+      <c r="S520" t="n">
+        <v>0</v>
+      </c>
+      <c r="T520" t="n">
+        <v>0</v>
+      </c>
+      <c r="U520" t="n">
+        <v>0</v>
+      </c>
+      <c r="V520" t="n">
+        <v>0</v>
+      </c>
+      <c r="W520" t="n">
+        <v>0</v>
+      </c>
+      <c r="X520" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:26.968902</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Gardabani - WIT Georgia</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>90</v>
+      </c>
+      <c r="E521" t="n">
+        <v>5</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0</v>
+      </c>
+      <c r="H521" t="n">
+        <v>0</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0</v>
+      </c>
+      <c r="J521" t="n">
+        <v>0</v>
+      </c>
+      <c r="K521" t="n">
+        <v>0</v>
+      </c>
+      <c r="L521" t="n">
+        <v>0</v>
+      </c>
+      <c r="M521" t="n">
+        <v>0</v>
+      </c>
+      <c r="N521" t="n">
+        <v>0</v>
+      </c>
+      <c r="O521" t="n">
+        <v>5</v>
+      </c>
+      <c r="P521" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>0</v>
+      </c>
+      <c r="R521" t="n">
+        <v>0</v>
+      </c>
+      <c r="S521" t="n">
+        <v>0</v>
+      </c>
+      <c r="T521" t="n">
+        <v>0</v>
+      </c>
+      <c r="U521" t="n">
+        <v>0</v>
+      </c>
+      <c r="V521" t="n">
+        <v>0</v>
+      </c>
+      <c r="W521" t="n">
+        <v>0</v>
+      </c>
+      <c r="X521" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:34.853881</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Guria - Lokomotivi Tbilisi</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>90</v>
+      </c>
+      <c r="E522" t="n">
+        <v>1</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>1</v>
+      </c>
+      <c r="P522" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>0</v>
+      </c>
+      <c r="R522" t="n">
+        <v>0</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>0</v>
+      </c>
+      <c r="U522" t="n">
+        <v>0</v>
+      </c>
+      <c r="V522" t="n">
+        <v>0</v>
+      </c>
+      <c r="W522" t="n">
+        <v>0</v>
+      </c>
+      <c r="X522" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:42.919804</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Iberia 2010 - Gonio</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>90</v>
+      </c>
+      <c r="E523" t="n">
+        <v>2</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="n">
+        <v>0</v>
+      </c>
+      <c r="M523" t="n">
+        <v>0</v>
+      </c>
+      <c r="N523" t="n">
+        <v>0</v>
+      </c>
+      <c r="O523" t="n">
+        <v>2</v>
+      </c>
+      <c r="P523" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>0</v>
+      </c>
+      <c r="R523" t="n">
+        <v>0</v>
+      </c>
+      <c r="S523" t="n">
+        <v>0</v>
+      </c>
+      <c r="T523" t="n">
+        <v>0</v>
+      </c>
+      <c r="U523" t="n">
+        <v>0</v>
+      </c>
+      <c r="V523" t="n">
+        <v>0</v>
+      </c>
+      <c r="W523" t="n">
+        <v>0</v>
+      </c>
+      <c r="X523" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:50.958465</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Kolkheti Khobi - Dinamo Tbilisi II</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>90</v>
+      </c>
+      <c r="E524" t="n">
+        <v>5</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0</v>
+      </c>
+      <c r="G524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" t="n">
+        <v>2</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" t="n">
+        <v>0</v>
+      </c>
+      <c r="M524" t="n">
+        <v>0</v>
+      </c>
+      <c r="N524" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" t="n">
+        <v>3</v>
+      </c>
+      <c r="P524" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>0</v>
+      </c>
+      <c r="R524" t="n">
+        <v>0</v>
+      </c>
+      <c r="S524" t="n">
+        <v>0</v>
+      </c>
+      <c r="T524" t="n">
+        <v>0</v>
+      </c>
+      <c r="U524" t="n">
+        <v>0</v>
+      </c>
+      <c r="V524" t="n">
+        <v>0</v>
+      </c>
+      <c r="W524" t="n">
+        <v>0</v>
+      </c>
+      <c r="X524" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:16:59.361240</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Margveti 2006 - Varketili</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>90</v>
+      </c>
+      <c r="E525" t="n">
+        <v>2</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>1</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0</v>
+      </c>
+      <c r="N525" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>1</v>
+      </c>
+      <c r="P525" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>0</v>
+      </c>
+      <c r="R525" t="n">
+        <v>0</v>
+      </c>
+      <c r="S525" t="n">
+        <v>0</v>
+      </c>
+      <c r="T525" t="n">
+        <v>0</v>
+      </c>
+      <c r="U525" t="n">
+        <v>0</v>
+      </c>
+      <c r="V525" t="n">
+        <v>0</v>
+      </c>
+      <c r="W525" t="n">
+        <v>0</v>
+      </c>
+      <c r="X525" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:17:07.302090</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Merani Tbilisi - Didube 2014</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>90</v>
+      </c>
+      <c r="E526" t="n">
+        <v>4</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" t="n">
+        <v>2</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>2</v>
+      </c>
+      <c r="P526" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>0</v>
+      </c>
+      <c r="R526" t="n">
+        <v>0</v>
+      </c>
+      <c r="S526" t="n">
+        <v>0</v>
+      </c>
+      <c r="T526" t="n">
+        <v>0</v>
+      </c>
+      <c r="U526" t="n">
+        <v>0</v>
+      </c>
+      <c r="V526" t="n">
+        <v>0</v>
+      </c>
+      <c r="W526" t="n">
+        <v>0</v>
+      </c>
+      <c r="X526" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:17:15.154386</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Aktobe Jas - Ekibastuz</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>90</v>
+      </c>
+      <c r="E527" t="n">
+        <v>2</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" t="n">
+        <v>0</v>
+      </c>
+      <c r="O527" t="n">
+        <v>2</v>
+      </c>
+      <c r="P527" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>0</v>
+      </c>
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="n">
+        <v>0</v>
+      </c>
+      <c r="T527" t="n">
+        <v>0</v>
+      </c>
+      <c r="U527" t="n">
+        <v>0</v>
+      </c>
+      <c r="V527" t="n">
+        <v>0</v>
+      </c>
+      <c r="W527" t="n">
+        <v>0</v>
+      </c>
+      <c r="X527" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:17:23.126870</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Shakhter Karagandy - Kaspij Aktau 2</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>90</v>
+      </c>
+      <c r="E528" t="n">
+        <v>1</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" t="n">
+        <v>0</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="n">
+        <v>1</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" t="n">
+        <v>0</v>
+      </c>
+      <c r="N528" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" t="n">
+        <v>0</v>
+      </c>
+      <c r="P528" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>0</v>
+      </c>
+      <c r="R528" t="n">
+        <v>0</v>
+      </c>
+      <c r="S528" t="n">
+        <v>0</v>
+      </c>
+      <c r="T528" t="n">
+        <v>0</v>
+      </c>
+      <c r="U528" t="n">
+        <v>0</v>
+      </c>
+      <c r="V528" t="n">
+        <v>0</v>
+      </c>
+      <c r="W528" t="n">
+        <v>0</v>
+      </c>
+      <c r="X528" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:17:31.235477</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Stabæk U19 - Fredrikstad FK U19</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>90</v>
+      </c>
+      <c r="E529" t="n">
+        <v>6</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" t="n">
+        <v>0</v>
+      </c>
+      <c r="I529" t="n">
+        <v>1</v>
+      </c>
+      <c r="J529" t="n">
+        <v>2</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" t="n">
+        <v>0</v>
+      </c>
+      <c r="M529" t="n">
+        <v>0</v>
+      </c>
+      <c r="N529" t="n">
+        <v>1</v>
+      </c>
+      <c r="O529" t="n">
+        <v>4</v>
+      </c>
+      <c r="P529" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>0</v>
+      </c>
+      <c r="R529" t="n">
+        <v>0</v>
+      </c>
+      <c r="S529" t="n">
+        <v>0</v>
+      </c>
+      <c r="T529" t="n">
+        <v>0</v>
+      </c>
+      <c r="U529" t="n">
+        <v>0</v>
+      </c>
+      <c r="V529" t="n">
+        <v>0</v>
+      </c>
+      <c r="W529" t="n">
+        <v>0</v>
+      </c>
+      <c r="X529" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:17:39.217016</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Persib Bandung - Persebaya Surabaya</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>120</v>
+      </c>
+      <c r="E530" t="n">
+        <v>2</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="n">
+        <v>1</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" t="n">
+        <v>0</v>
+      </c>
+      <c r="N530" t="n">
+        <v>0</v>
+      </c>
+      <c r="O530" t="n">
+        <v>1</v>
+      </c>
+      <c r="P530" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>0</v>
+      </c>
+      <c r="R530" t="n">
+        <v>0</v>
+      </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
+      <c r="T530" t="n">
+        <v>0</v>
+      </c>
+      <c r="U530" t="n">
+        <v>0</v>
+      </c>
+      <c r="V530" t="n">
+        <v>0</v>
+      </c>
+      <c r="W530" t="n">
+        <v>0</v>
+      </c>
+      <c r="X530" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:17:47.301890</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Sogdiana - Andijan</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>90</v>
+      </c>
+      <c r="E531" t="n">
+        <v>1</v>
+      </c>
+      <c r="F531" t="n">
+        <v>8</v>
+      </c>
+      <c r="G531" t="n">
+        <v>13</v>
+      </c>
+      <c r="H531" t="n">
+        <v>8</v>
+      </c>
+      <c r="I531" t="n">
+        <v>1</v>
+      </c>
+      <c r="J531" t="n">
+        <v>1</v>
+      </c>
+      <c r="K531" t="n">
+        <v>5</v>
+      </c>
+      <c r="L531" t="n">
+        <v>8</v>
+      </c>
+      <c r="M531" t="n">
+        <v>5</v>
+      </c>
+      <c r="N531" t="n">
+        <v>1</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>5</v>
+      </c>
+      <c r="R531" t="n">
+        <v>3</v>
+      </c>
+      <c r="S531" t="n">
+        <v>0</v>
+      </c>
+      <c r="T531" t="n">
+        <v>0</v>
+      </c>
+      <c r="U531" t="n">
+        <v>0</v>
+      </c>
+      <c r="V531" t="n">
+        <v>0</v>
+      </c>
+      <c r="W531" t="n">
+        <v>0</v>
+      </c>
+      <c r="X531" t="n">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
